--- a/AAII_Financials/Yearly/HLTOY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HLTOY_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
   <si>
     <t>HLTOY</t>
   </si>
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>3749000</v>
+        <v>3774500</v>
       </c>
       <c r="E8" s="3">
-        <v>3619900</v>
+        <v>3759700</v>
       </c>
       <c r="F8" s="3">
-        <v>3535900</v>
+        <v>3630200</v>
       </c>
       <c r="G8" s="3">
-        <v>3583800</v>
+        <v>3546000</v>
       </c>
       <c r="H8" s="3">
-        <v>4121600</v>
+        <v>3594000</v>
       </c>
       <c r="I8" s="3">
-        <v>4119600</v>
+        <v>4133400</v>
       </c>
       <c r="J8" s="3">
+        <v>4131400</v>
+      </c>
+      <c r="K8" s="3">
         <v>4240300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3984100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4424300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4849500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4754700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5914000</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>237700</v>
+        <v>352800</v>
       </c>
       <c r="E9" s="3">
-        <v>187100</v>
+        <v>238400</v>
       </c>
       <c r="F9" s="3">
-        <v>178500</v>
+        <v>187600</v>
       </c>
       <c r="G9" s="3">
-        <v>151800</v>
+        <v>179000</v>
       </c>
       <c r="H9" s="3">
-        <v>163400</v>
+        <v>152200</v>
       </c>
       <c r="I9" s="3">
-        <v>177400</v>
+        <v>163900</v>
       </c>
       <c r="J9" s="3">
+        <v>177900</v>
+      </c>
+      <c r="K9" s="3">
         <v>194100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>168300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>146400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>148100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1009900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1272100</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>3511300</v>
+        <v>3421700</v>
       </c>
       <c r="E10" s="3">
-        <v>3432800</v>
+        <v>3521300</v>
       </c>
       <c r="F10" s="3">
-        <v>3357400</v>
+        <v>3442600</v>
       </c>
       <c r="G10" s="3">
-        <v>3432000</v>
+        <v>3367000</v>
       </c>
       <c r="H10" s="3">
-        <v>3958200</v>
+        <v>3441800</v>
       </c>
       <c r="I10" s="3">
-        <v>3942200</v>
+        <v>3969500</v>
       </c>
       <c r="J10" s="3">
+        <v>3953500</v>
+      </c>
+      <c r="K10" s="3">
         <v>4046200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3815800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4277800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4701400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3744700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4641900</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,8 +873,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -902,9 +915,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,93 +960,102 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="E14" s="3">
-        <v>54700</v>
+        <v>0</v>
       </c>
       <c r="F14" s="3">
-        <v>-10600</v>
+        <v>54800</v>
       </c>
       <c r="G14" s="3">
-        <v>45400</v>
+        <v>-10700</v>
       </c>
       <c r="H14" s="3">
+        <v>45500</v>
+      </c>
+      <c r="I14" s="3">
         <v>-2400</v>
       </c>
-      <c r="I14" s="3">
-        <v>43200</v>
-      </c>
       <c r="J14" s="3">
+        <v>43300</v>
+      </c>
+      <c r="K14" s="3">
         <v>-19900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>20300</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-100</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>862700</v>
+        <v>725200</v>
       </c>
       <c r="E15" s="3">
-        <v>724300</v>
+        <v>865100</v>
       </c>
       <c r="F15" s="3">
-        <v>881100</v>
+        <v>726400</v>
       </c>
       <c r="G15" s="3">
-        <v>1237600</v>
+        <v>883600</v>
       </c>
       <c r="H15" s="3">
-        <v>884800</v>
+        <v>1241100</v>
       </c>
       <c r="I15" s="3">
-        <v>952800</v>
+        <v>887300</v>
       </c>
       <c r="J15" s="3">
+        <v>955600</v>
+      </c>
+      <c r="K15" s="3">
         <v>956300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>846700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>899200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1007800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>898600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1537900</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3108300</v>
+        <v>2994800</v>
       </c>
       <c r="E17" s="3">
-        <v>2793200</v>
+        <v>3117200</v>
       </c>
       <c r="F17" s="3">
-        <v>3165700</v>
+        <v>2801200</v>
       </c>
       <c r="G17" s="3">
-        <v>3058300</v>
+        <v>3174700</v>
       </c>
       <c r="H17" s="3">
-        <v>3581900</v>
+        <v>3067000</v>
       </c>
       <c r="I17" s="3">
-        <v>3668600</v>
+        <v>3592100</v>
       </c>
       <c r="J17" s="3">
+        <v>3679100</v>
+      </c>
+      <c r="K17" s="3">
         <v>3802100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3605200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3759100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4448200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4123900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5500100</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>640700</v>
+        <v>779700</v>
       </c>
       <c r="E18" s="3">
-        <v>826700</v>
+        <v>642500</v>
       </c>
       <c r="F18" s="3">
-        <v>370200</v>
+        <v>829000</v>
       </c>
       <c r="G18" s="3">
-        <v>525500</v>
+        <v>371300</v>
       </c>
       <c r="H18" s="3">
-        <v>539700</v>
+        <v>527000</v>
       </c>
       <c r="I18" s="3">
-        <v>451000</v>
+        <v>541200</v>
       </c>
       <c r="J18" s="3">
+        <v>452300</v>
+      </c>
+      <c r="K18" s="3">
         <v>438200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>378900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>665200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>401300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>630800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>413900</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,218 +1178,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E20" s="3">
         <v>4700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2100</v>
       </c>
-      <c r="G20" s="3">
-        <v>19400</v>
-      </c>
       <c r="H20" s="3">
+        <v>19500</v>
+      </c>
+      <c r="I20" s="3">
         <v>2300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-4200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>33400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>10200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>273100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>265800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>61700</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1507700</v>
+        <v>1503300</v>
       </c>
       <c r="E21" s="3">
-        <v>1553500</v>
+        <v>1517500</v>
       </c>
       <c r="F21" s="3">
-        <v>1271800</v>
+        <v>1562500</v>
       </c>
       <c r="G21" s="3">
-        <v>1854600</v>
+        <v>1281200</v>
       </c>
       <c r="H21" s="3">
-        <v>1361600</v>
+        <v>1868300</v>
       </c>
       <c r="I21" s="3">
-        <v>1357800</v>
+        <v>1370700</v>
       </c>
       <c r="J21" s="3">
+        <v>1367400</v>
+      </c>
+      <c r="K21" s="3">
         <v>1391900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1242600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1576600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1678100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1796600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2014600</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>43300</v>
+        <v>12600</v>
       </c>
       <c r="E22" s="3">
-        <v>48800</v>
+        <v>43400</v>
       </c>
       <c r="F22" s="3">
-        <v>61000</v>
+        <v>49000</v>
       </c>
       <c r="G22" s="3">
-        <v>100700</v>
+        <v>61200</v>
       </c>
       <c r="H22" s="3">
-        <v>93400</v>
+        <v>101000</v>
       </c>
       <c r="I22" s="3">
-        <v>150900</v>
+        <v>93700</v>
       </c>
       <c r="J22" s="3">
+        <v>151400</v>
+      </c>
+      <c r="K22" s="3">
         <v>162100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>160700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>228900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>297900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>271500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>340500</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>602100</v>
+        <v>761100</v>
       </c>
       <c r="E23" s="3">
-        <v>780500</v>
+        <v>603800</v>
       </c>
       <c r="F23" s="3">
-        <v>307200</v>
+        <v>782800</v>
       </c>
       <c r="G23" s="3">
-        <v>444200</v>
+        <v>308000</v>
       </c>
       <c r="H23" s="3">
-        <v>448500</v>
+        <v>445500</v>
       </c>
       <c r="I23" s="3">
-        <v>295900</v>
+        <v>449800</v>
       </c>
       <c r="J23" s="3">
+        <v>296700</v>
+      </c>
+      <c r="K23" s="3">
         <v>273900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>251600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>446400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>376600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>625100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>135100</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>180300</v>
+        <v>182600</v>
       </c>
       <c r="E24" s="3">
-        <v>253500</v>
+        <v>180800</v>
       </c>
       <c r="F24" s="3">
-        <v>49800</v>
+        <v>254200</v>
       </c>
       <c r="G24" s="3">
-        <v>100100</v>
+        <v>49900</v>
       </c>
       <c r="H24" s="3">
-        <v>179900</v>
+        <v>100400</v>
       </c>
       <c r="I24" s="3">
-        <v>160100</v>
+        <v>180400</v>
       </c>
       <c r="J24" s="3">
+        <v>160600</v>
+      </c>
+      <c r="K24" s="3">
         <v>182700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>120300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>139900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>25000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>114100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>151100</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>421700</v>
+        <v>578500</v>
       </c>
       <c r="E26" s="3">
-        <v>527100</v>
+        <v>422900</v>
       </c>
       <c r="F26" s="3">
-        <v>257400</v>
+        <v>528600</v>
       </c>
       <c r="G26" s="3">
-        <v>344100</v>
+        <v>258100</v>
       </c>
       <c r="H26" s="3">
-        <v>268600</v>
+        <v>345000</v>
       </c>
       <c r="I26" s="3">
-        <v>135700</v>
+        <v>269400</v>
       </c>
       <c r="J26" s="3">
+        <v>136100</v>
+      </c>
+      <c r="K26" s="3">
         <v>91100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>131400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>306600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>351600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>511000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-16000</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>421600</v>
+        <v>578500</v>
       </c>
       <c r="E27" s="3">
-        <v>492300</v>
+        <v>422800</v>
       </c>
       <c r="F27" s="3">
-        <v>240200</v>
+        <v>493700</v>
       </c>
       <c r="G27" s="3">
-        <v>520000</v>
+        <v>240900</v>
       </c>
       <c r="H27" s="3">
-        <v>278500</v>
+        <v>521500</v>
       </c>
       <c r="I27" s="3">
-        <v>183900</v>
+        <v>279300</v>
       </c>
       <c r="J27" s="3">
+        <v>184400</v>
+      </c>
+      <c r="K27" s="3">
         <v>151900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>155100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>301900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>344300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>483300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>140500</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,51 +1580,57 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E29" s="3">
-        <v>112700</v>
+        <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>150300</v>
+        <v>113100</v>
       </c>
       <c r="G29" s="3">
-        <v>-297500</v>
+        <v>150700</v>
       </c>
       <c r="H29" s="3">
-        <v>-88600</v>
+        <v>-298400</v>
       </c>
       <c r="I29" s="3">
-        <v>-111000</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>8</v>
+        <v>-88900</v>
+      </c>
+      <c r="J29" s="3">
+        <v>-111300</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="L29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>34600</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>34800</v>
       </c>
-      <c r="O29" s="3" t="s">
+      <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2100</v>
       </c>
-      <c r="G32" s="3">
-        <v>-19400</v>
-      </c>
       <c r="H32" s="3">
+        <v>-19500</v>
+      </c>
+      <c r="I32" s="3">
         <v>-2300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>4200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-33400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-10200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-273100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-265800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-61700</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>421600</v>
+        <v>578500</v>
       </c>
       <c r="E33" s="3">
-        <v>605000</v>
+        <v>422800</v>
       </c>
       <c r="F33" s="3">
-        <v>390500</v>
+        <v>606700</v>
       </c>
       <c r="G33" s="3">
-        <v>222500</v>
+        <v>391600</v>
       </c>
       <c r="H33" s="3">
-        <v>189900</v>
+        <v>223200</v>
       </c>
       <c r="I33" s="3">
-        <v>72900</v>
+        <v>190400</v>
       </c>
       <c r="J33" s="3">
+        <v>73100</v>
+      </c>
+      <c r="K33" s="3">
         <v>151900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>155100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>301900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>378800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>518100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>140500</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>421600</v>
+        <v>578500</v>
       </c>
       <c r="E35" s="3">
-        <v>605000</v>
+        <v>422800</v>
       </c>
       <c r="F35" s="3">
-        <v>390500</v>
+        <v>606700</v>
       </c>
       <c r="G35" s="3">
-        <v>222500</v>
+        <v>391600</v>
       </c>
       <c r="H35" s="3">
-        <v>189900</v>
+        <v>223200</v>
       </c>
       <c r="I35" s="3">
-        <v>72900</v>
+        <v>190400</v>
       </c>
       <c r="J35" s="3">
+        <v>73100</v>
+      </c>
+      <c r="K35" s="3">
         <v>151900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>155100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>301900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>378800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>518100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>140500</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,386 +1986,414 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>640300</v>
+        <v>504800</v>
       </c>
       <c r="E41" s="3">
-        <v>684300</v>
+        <v>642100</v>
       </c>
       <c r="F41" s="3">
-        <v>560100</v>
+        <v>686300</v>
       </c>
       <c r="G41" s="3">
-        <v>1148300</v>
+        <v>561700</v>
       </c>
       <c r="H41" s="3">
-        <v>1176900</v>
+        <v>1151500</v>
       </c>
       <c r="I41" s="3">
-        <v>1408000</v>
+        <v>1180300</v>
       </c>
       <c r="J41" s="3">
+        <v>1412000</v>
+      </c>
+      <c r="K41" s="3">
         <v>1720400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1350000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1704800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3455300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1278500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4600</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E42" s="3">
         <v>5200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>6100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>5900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>6200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>5500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>6400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>6100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>6900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>19700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1286700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1212500</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>592500</v>
+        <v>684200</v>
       </c>
       <c r="E43" s="3">
-        <v>654100</v>
+        <v>594200</v>
       </c>
       <c r="F43" s="3">
-        <v>556300</v>
+        <v>656000</v>
       </c>
       <c r="G43" s="3">
-        <v>779500</v>
+        <v>557900</v>
       </c>
       <c r="H43" s="3">
-        <v>786400</v>
+        <v>781700</v>
       </c>
       <c r="I43" s="3">
-        <v>780900</v>
+        <v>788700</v>
       </c>
       <c r="J43" s="3">
+        <v>783100</v>
+      </c>
+      <c r="K43" s="3">
         <v>792600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>743800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>773300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1682600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1007700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1203500</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>58600</v>
+        <v>64100</v>
       </c>
       <c r="E44" s="3">
-        <v>41200</v>
+        <v>58800</v>
       </c>
       <c r="F44" s="3">
-        <v>29200</v>
+        <v>41300</v>
       </c>
       <c r="G44" s="3">
-        <v>55700</v>
+        <v>29300</v>
       </c>
       <c r="H44" s="3">
-        <v>89000</v>
+        <v>55800</v>
       </c>
       <c r="I44" s="3">
-        <v>99100</v>
+        <v>89200</v>
       </c>
       <c r="J44" s="3">
+        <v>99300</v>
+      </c>
+      <c r="K44" s="3">
         <v>104100</v>
-      </c>
-      <c r="K44" s="3">
-        <v>99200</v>
       </c>
       <c r="L44" s="3">
         <v>99200</v>
       </c>
       <c r="M44" s="3">
+        <v>99200</v>
+      </c>
+      <c r="N44" s="3">
         <v>232100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>244600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>146700</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>108700</v>
+        <v>83800</v>
       </c>
       <c r="E45" s="3">
-        <v>124600</v>
+        <v>65900</v>
       </c>
       <c r="F45" s="3">
-        <v>103300</v>
+        <v>124900</v>
       </c>
       <c r="G45" s="3">
-        <v>155600</v>
+        <v>103600</v>
       </c>
       <c r="H45" s="3">
-        <v>180100</v>
+        <v>156000</v>
       </c>
       <c r="I45" s="3">
-        <v>286000</v>
+        <v>180600</v>
       </c>
       <c r="J45" s="3">
+        <v>286800</v>
+      </c>
+      <c r="K45" s="3">
         <v>337700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>260500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>234300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>552000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>497900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>136600</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1405300</v>
+        <v>1342900</v>
       </c>
       <c r="E46" s="3">
-        <v>1510300</v>
+        <v>1366200</v>
       </c>
       <c r="F46" s="3">
-        <v>1254700</v>
+        <v>1514600</v>
       </c>
       <c r="G46" s="3">
-        <v>2145200</v>
+        <v>1258300</v>
       </c>
       <c r="H46" s="3">
-        <v>2237900</v>
+        <v>2151300</v>
       </c>
       <c r="I46" s="3">
-        <v>2580300</v>
+        <v>2244300</v>
       </c>
       <c r="J46" s="3">
+        <v>2587700</v>
+      </c>
+      <c r="K46" s="3">
         <v>2960700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2460400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2815900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2983400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2614700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2704000</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>103100</v>
+        <v>97400</v>
       </c>
       <c r="E47" s="3">
-        <v>101000</v>
+        <v>103400</v>
       </c>
       <c r="F47" s="3">
-        <v>105500</v>
+        <v>101300</v>
       </c>
       <c r="G47" s="3">
-        <v>135700</v>
+        <v>105800</v>
       </c>
       <c r="H47" s="3">
-        <v>177800</v>
+        <v>136100</v>
       </c>
       <c r="I47" s="3">
-        <v>89600</v>
+        <v>178300</v>
       </c>
       <c r="J47" s="3">
+        <v>89900</v>
+      </c>
+      <c r="K47" s="3">
         <v>93000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>90100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>118100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>132800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>243500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>169600</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2547300</v>
+        <v>2662300</v>
       </c>
       <c r="E48" s="3">
-        <v>2544300</v>
+        <v>2554500</v>
       </c>
       <c r="F48" s="3">
-        <v>2628600</v>
+        <v>2551600</v>
       </c>
       <c r="G48" s="3">
-        <v>2994500</v>
+        <v>2636100</v>
       </c>
       <c r="H48" s="3">
-        <v>2974100</v>
+        <v>3003000</v>
       </c>
       <c r="I48" s="3">
-        <v>2973900</v>
+        <v>2982600</v>
       </c>
       <c r="J48" s="3">
+        <v>2982400</v>
+      </c>
+      <c r="K48" s="3">
         <v>3095000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3012000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3503900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7844400</v>
       </c>
-      <c r="N48" s="3" t="s">
+      <c r="O48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5080200</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1093500</v>
+        <v>983300</v>
       </c>
       <c r="E49" s="3">
-        <v>1207800</v>
+        <v>1096600</v>
       </c>
       <c r="F49" s="3">
-        <v>1243000</v>
+        <v>1211300</v>
       </c>
       <c r="G49" s="3">
-        <v>1224000</v>
+        <v>1246500</v>
       </c>
       <c r="H49" s="3">
-        <v>1440400</v>
+        <v>1227500</v>
       </c>
       <c r="I49" s="3">
-        <v>1600300</v>
+        <v>1444600</v>
       </c>
       <c r="J49" s="3">
+        <v>1604800</v>
+      </c>
+      <c r="K49" s="3">
         <v>1615200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1615700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1862500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2953200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3338100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1767200</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>275000</v>
+        <v>285400</v>
       </c>
       <c r="E52" s="3">
-        <v>297000</v>
+        <v>275800</v>
       </c>
       <c r="F52" s="3">
-        <v>1134900</v>
+        <v>297800</v>
       </c>
       <c r="G52" s="3">
-        <v>396900</v>
+        <v>1138200</v>
       </c>
       <c r="H52" s="3">
-        <v>439100</v>
+        <v>398000</v>
       </c>
       <c r="I52" s="3">
-        <v>461800</v>
+        <v>440400</v>
       </c>
       <c r="J52" s="3">
+        <v>463100</v>
+      </c>
+      <c r="K52" s="3">
         <v>451300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>437100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>511500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>564500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>676100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>950000</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>5424100</v>
+        <v>5371300</v>
       </c>
       <c r="E54" s="3">
-        <v>5660400</v>
+        <v>5396500</v>
       </c>
       <c r="F54" s="3">
-        <v>6366700</v>
+        <v>5676600</v>
       </c>
       <c r="G54" s="3">
-        <v>6896300</v>
+        <v>6384900</v>
       </c>
       <c r="H54" s="3">
-        <v>7269400</v>
+        <v>6916000</v>
       </c>
       <c r="I54" s="3">
-        <v>7705900</v>
+        <v>7290200</v>
       </c>
       <c r="J54" s="3">
+        <v>7727900</v>
+      </c>
+      <c r="K54" s="3">
         <v>8215200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7615400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8811800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>9382200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>9185900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>10671000</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,260 +2654,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>948300</v>
+        <v>942700</v>
       </c>
       <c r="E57" s="3">
-        <v>888100</v>
+        <v>951000</v>
       </c>
       <c r="F57" s="3">
-        <v>781000</v>
+        <v>890600</v>
       </c>
       <c r="G57" s="3">
-        <v>1015600</v>
+        <v>783200</v>
       </c>
       <c r="H57" s="3">
-        <v>1121900</v>
+        <v>1018500</v>
       </c>
       <c r="I57" s="3">
-        <v>1261200</v>
+        <v>1125100</v>
       </c>
       <c r="J57" s="3">
+        <v>1264800</v>
+      </c>
+      <c r="K57" s="3">
         <v>1480000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1227500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1101000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1104900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>861400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>879900</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>270400</v>
+        <v>66200</v>
       </c>
       <c r="E58" s="3">
-        <v>508900</v>
+        <v>271200</v>
       </c>
       <c r="F58" s="3">
-        <v>314900</v>
+        <v>510300</v>
       </c>
       <c r="G58" s="3">
-        <v>845500</v>
+        <v>315800</v>
       </c>
       <c r="H58" s="3">
-        <v>594600</v>
+        <v>848000</v>
       </c>
       <c r="I58" s="3">
-        <v>829500</v>
+        <v>596300</v>
       </c>
       <c r="J58" s="3">
+        <v>831900</v>
+      </c>
+      <c r="K58" s="3">
         <v>199700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>442500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>525500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>478400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1554300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>895500</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>741900</v>
+        <v>785200</v>
       </c>
       <c r="E59" s="3">
-        <v>705600</v>
+        <v>701000</v>
       </c>
       <c r="F59" s="3">
-        <v>806800</v>
+        <v>707600</v>
       </c>
       <c r="G59" s="3">
-        <v>762900</v>
+        <v>809100</v>
       </c>
       <c r="H59" s="3">
-        <v>817900</v>
+        <v>765000</v>
       </c>
       <c r="I59" s="3">
-        <v>861600</v>
+        <v>820200</v>
       </c>
       <c r="J59" s="3">
+        <v>864100</v>
+      </c>
+      <c r="K59" s="3">
         <v>967800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>870600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1122800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1296700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1550400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1110200</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1960600</v>
+        <v>1794100</v>
       </c>
       <c r="E60" s="3">
-        <v>2102500</v>
+        <v>1923100</v>
       </c>
       <c r="F60" s="3">
-        <v>1902700</v>
+        <v>2108500</v>
       </c>
       <c r="G60" s="3">
-        <v>2624000</v>
+        <v>1908100</v>
       </c>
       <c r="H60" s="3">
-        <v>2534300</v>
+        <v>2631500</v>
       </c>
       <c r="I60" s="3">
-        <v>2952300</v>
+        <v>2541600</v>
       </c>
       <c r="J60" s="3">
+        <v>2960700</v>
+      </c>
+      <c r="K60" s="3">
         <v>2647600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2540700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2749200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2880000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3367700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2885600</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1154000</v>
+        <v>1123600</v>
       </c>
       <c r="E61" s="3">
-        <v>1023000</v>
+        <v>1157300</v>
       </c>
       <c r="F61" s="3">
-        <v>1373000</v>
+        <v>1026000</v>
       </c>
       <c r="G61" s="3">
-        <v>1444000</v>
+        <v>1376900</v>
       </c>
       <c r="H61" s="3">
-        <v>1389500</v>
+        <v>1448200</v>
       </c>
       <c r="I61" s="3">
-        <v>1384700</v>
+        <v>1393400</v>
       </c>
       <c r="J61" s="3">
+        <v>1388600</v>
+      </c>
+      <c r="K61" s="3">
         <v>2106000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1792100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2453600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3058100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2893400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4858500</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>303500</v>
+        <v>338600</v>
       </c>
       <c r="E62" s="3">
-        <v>395000</v>
+        <v>304300</v>
       </c>
       <c r="F62" s="3">
-        <v>431700</v>
+        <v>396200</v>
       </c>
       <c r="G62" s="3">
-        <v>459600</v>
+        <v>433000</v>
       </c>
       <c r="H62" s="3">
-        <v>510100</v>
+        <v>460900</v>
       </c>
       <c r="I62" s="3">
-        <v>559400</v>
+        <v>511500</v>
       </c>
       <c r="J62" s="3">
+        <v>561000</v>
+      </c>
+      <c r="K62" s="3">
         <v>584500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>619100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>788000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>858000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>868400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>864200</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>3418600</v>
+        <v>3256800</v>
       </c>
       <c r="E66" s="3">
-        <v>3522500</v>
+        <v>3385300</v>
       </c>
       <c r="F66" s="3">
-        <v>4201200</v>
+        <v>3532500</v>
       </c>
       <c r="G66" s="3">
-        <v>4669800</v>
+        <v>4213200</v>
       </c>
       <c r="H66" s="3">
-        <v>4737900</v>
+        <v>4683200</v>
       </c>
       <c r="I66" s="3">
-        <v>5162200</v>
+        <v>4751400</v>
       </c>
       <c r="J66" s="3">
+        <v>5177000</v>
+      </c>
+      <c r="K66" s="3">
         <v>5658900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5311400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6415900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7085100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7430400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9047000</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>4018400</v>
+        <v>541100</v>
       </c>
       <c r="E72" s="3">
-        <v>4144300</v>
+        <v>423800</v>
       </c>
       <c r="F72" s="3">
-        <v>4130500</v>
+        <v>4156100</v>
       </c>
       <c r="G72" s="3">
-        <v>4094400</v>
+        <v>4142300</v>
       </c>
       <c r="H72" s="3">
-        <v>4320900</v>
+        <v>4106100</v>
       </c>
       <c r="I72" s="3">
-        <v>4111600</v>
+        <v>4333200</v>
       </c>
       <c r="J72" s="3">
+        <v>4123400</v>
+      </c>
+      <c r="K72" s="3">
         <v>4124200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3779400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4027600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4004500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6941000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3466400</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2005500</v>
+        <v>2114500</v>
       </c>
       <c r="E76" s="3">
-        <v>2138000</v>
+        <v>2011200</v>
       </c>
       <c r="F76" s="3">
-        <v>2165400</v>
+        <v>2144100</v>
       </c>
       <c r="G76" s="3">
-        <v>2226400</v>
+        <v>2171600</v>
       </c>
       <c r="H76" s="3">
-        <v>2531500</v>
+        <v>2232800</v>
       </c>
       <c r="I76" s="3">
-        <v>2543700</v>
+        <v>2538800</v>
       </c>
       <c r="J76" s="3">
+        <v>2550900</v>
+      </c>
+      <c r="K76" s="3">
         <v>2556300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2303900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2396000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2297100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1755500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1624000</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>421600</v>
+        <v>578500</v>
       </c>
       <c r="E81" s="3">
-        <v>605000</v>
+        <v>422800</v>
       </c>
       <c r="F81" s="3">
-        <v>390500</v>
+        <v>606700</v>
       </c>
       <c r="G81" s="3">
-        <v>222500</v>
+        <v>391600</v>
       </c>
       <c r="H81" s="3">
-        <v>189900</v>
+        <v>223200</v>
       </c>
       <c r="I81" s="3">
-        <v>72900</v>
+        <v>190400</v>
       </c>
       <c r="J81" s="3">
+        <v>73100</v>
+      </c>
+      <c r="K81" s="3">
         <v>151900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>155100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>301900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>378800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>518100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>140500</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>862700</v>
+        <v>725200</v>
       </c>
       <c r="E83" s="3">
-        <v>724300</v>
+        <v>865100</v>
       </c>
       <c r="F83" s="3">
-        <v>904000</v>
+        <v>726400</v>
       </c>
       <c r="G83" s="3">
-        <v>1310200</v>
+        <v>906600</v>
       </c>
       <c r="H83" s="3">
-        <v>819900</v>
+        <v>1314000</v>
       </c>
       <c r="I83" s="3">
-        <v>911300</v>
+        <v>822300</v>
       </c>
       <c r="J83" s="3">
+        <v>913900</v>
+      </c>
+      <c r="K83" s="3">
         <v>956300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>846700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>899200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1007800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>898600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1537900</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1429200</v>
+        <v>1300400</v>
       </c>
       <c r="E89" s="3">
-        <v>1407800</v>
+        <v>1433200</v>
       </c>
       <c r="F89" s="3">
-        <v>1274400</v>
+        <v>1411800</v>
       </c>
       <c r="G89" s="3">
-        <v>1258900</v>
+        <v>1278100</v>
       </c>
       <c r="H89" s="3">
-        <v>1072000</v>
+        <v>1262500</v>
       </c>
       <c r="I89" s="3">
-        <v>868700</v>
+        <v>1075000</v>
       </c>
       <c r="J89" s="3">
+        <v>871100</v>
+      </c>
+      <c r="K89" s="3">
         <v>1112200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>962800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1128800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1306100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1281300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1418200</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-693900</v>
+        <v>-676100</v>
       </c>
       <c r="E91" s="3">
-        <v>-635800</v>
+        <v>-695800</v>
       </c>
       <c r="F91" s="3">
-        <v>-724600</v>
+        <v>-637600</v>
       </c>
       <c r="G91" s="3">
-        <v>-718100</v>
+        <v>-726600</v>
       </c>
       <c r="H91" s="3">
-        <v>-781100</v>
+        <v>-720100</v>
       </c>
       <c r="I91" s="3">
-        <v>-981100</v>
+        <v>-783300</v>
       </c>
       <c r="J91" s="3">
+        <v>-983900</v>
+      </c>
+      <c r="K91" s="3">
         <v>-708500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-672100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-681900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-723300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1166300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-841000</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-692800</v>
+        <v>-658100</v>
       </c>
       <c r="E94" s="3">
-        <v>-472500</v>
+        <v>-694800</v>
       </c>
       <c r="F94" s="3">
-        <v>-792200</v>
+        <v>-473900</v>
       </c>
       <c r="G94" s="3">
-        <v>-684200</v>
+        <v>-794400</v>
       </c>
       <c r="H94" s="3">
-        <v>-782600</v>
+        <v>-686200</v>
       </c>
       <c r="I94" s="3">
-        <v>-990300</v>
+        <v>-784800</v>
       </c>
       <c r="J94" s="3">
+        <v>-993100</v>
+      </c>
+      <c r="K94" s="3">
         <v>-702000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-658800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-650400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>191800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>165100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1210200</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,35 +4220,36 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-271100</v>
+        <v>-271900</v>
       </c>
       <c r="E96" s="3">
-        <v>-462300</v>
+        <v>-271900</v>
       </c>
       <c r="F96" s="3">
-        <v>-279800</v>
+        <v>-463600</v>
       </c>
       <c r="G96" s="3">
-        <v>-270200</v>
+        <v>-280600</v>
       </c>
       <c r="H96" s="3">
-        <v>-185600</v>
+        <v>-270900</v>
       </c>
       <c r="I96" s="3">
-        <v>-84700</v>
+        <v>-186200</v>
       </c>
       <c r="J96" s="3">
+        <v>-85000</v>
+      </c>
+      <c r="K96" s="3">
         <v>-53100</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -4029,9 +4262,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-782700</v>
+        <v>-779400</v>
       </c>
       <c r="E100" s="3">
-        <v>-810000</v>
+        <v>-785000</v>
       </c>
       <c r="F100" s="3">
-        <v>-1067400</v>
+        <v>-812300</v>
       </c>
       <c r="G100" s="3">
-        <v>-601200</v>
+        <v>-1070500</v>
       </c>
       <c r="H100" s="3">
-        <v>-520800</v>
+        <v>-602900</v>
       </c>
       <c r="I100" s="3">
-        <v>-185600</v>
+        <v>-522300</v>
       </c>
       <c r="J100" s="3">
+        <v>-186200</v>
+      </c>
+      <c r="K100" s="3">
         <v>-124100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-500300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-403700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1155800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-914600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-581200</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E101" s="3">
         <v>2300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-3000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-2200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-5100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>5000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-3900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-6700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3500</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-44100</v>
+        <v>-137300</v>
       </c>
       <c r="E102" s="3">
-        <v>124200</v>
+        <v>-44200</v>
       </c>
       <c r="F102" s="3">
-        <v>-588200</v>
+        <v>124600</v>
       </c>
       <c r="G102" s="3">
-        <v>-28600</v>
+        <v>-589900</v>
       </c>
       <c r="H102" s="3">
-        <v>-231100</v>
+        <v>-28700</v>
       </c>
       <c r="I102" s="3">
-        <v>-312400</v>
+        <v>-231800</v>
       </c>
       <c r="J102" s="3">
+        <v>-313300</v>
+      </c>
+      <c r="K102" s="3">
         <v>285500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-191300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>74100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>338200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>525100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-376700</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/HLTOY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HLTOY_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>3774500</v>
+        <v>3748800</v>
       </c>
       <c r="E8" s="3">
-        <v>3759700</v>
+        <v>3734100</v>
       </c>
       <c r="F8" s="3">
-        <v>3630200</v>
+        <v>3605500</v>
       </c>
       <c r="G8" s="3">
-        <v>3546000</v>
+        <v>3521900</v>
       </c>
       <c r="H8" s="3">
-        <v>3594000</v>
+        <v>3569600</v>
       </c>
       <c r="I8" s="3">
-        <v>4133400</v>
+        <v>4105300</v>
       </c>
       <c r="J8" s="3">
-        <v>4131400</v>
+        <v>4103300</v>
       </c>
       <c r="K8" s="3">
         <v>4240300</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>352800</v>
+        <v>350400</v>
       </c>
       <c r="E9" s="3">
-        <v>238400</v>
+        <v>236800</v>
       </c>
       <c r="F9" s="3">
-        <v>187600</v>
+        <v>186300</v>
       </c>
       <c r="G9" s="3">
-        <v>179000</v>
+        <v>177800</v>
       </c>
       <c r="H9" s="3">
-        <v>152200</v>
+        <v>151200</v>
       </c>
       <c r="I9" s="3">
-        <v>163900</v>
+        <v>162800</v>
       </c>
       <c r="J9" s="3">
-        <v>177900</v>
+        <v>176700</v>
       </c>
       <c r="K9" s="3">
         <v>194100</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>3421700</v>
+        <v>3398500</v>
       </c>
       <c r="E10" s="3">
-        <v>3521300</v>
+        <v>3497400</v>
       </c>
       <c r="F10" s="3">
-        <v>3442600</v>
+        <v>3419200</v>
       </c>
       <c r="G10" s="3">
-        <v>3367000</v>
+        <v>3344100</v>
       </c>
       <c r="H10" s="3">
-        <v>3441800</v>
+        <v>3418400</v>
       </c>
       <c r="I10" s="3">
-        <v>3969500</v>
+        <v>3942500</v>
       </c>
       <c r="J10" s="3">
-        <v>3953500</v>
+        <v>3926600</v>
       </c>
       <c r="K10" s="3">
         <v>4046200</v>
@@ -976,19 +976,19 @@
         <v>0</v>
       </c>
       <c r="F14" s="3">
-        <v>54800</v>
+        <v>54500</v>
       </c>
       <c r="G14" s="3">
-        <v>-10700</v>
+        <v>-10600</v>
       </c>
       <c r="H14" s="3">
-        <v>45500</v>
+        <v>45200</v>
       </c>
       <c r="I14" s="3">
         <v>-2400</v>
       </c>
       <c r="J14" s="3">
-        <v>43300</v>
+        <v>43000</v>
       </c>
       <c r="K14" s="3">
         <v>-19900</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>725200</v>
+        <v>720300</v>
       </c>
       <c r="E15" s="3">
-        <v>865100</v>
+        <v>859300</v>
       </c>
       <c r="F15" s="3">
-        <v>726400</v>
+        <v>721500</v>
       </c>
       <c r="G15" s="3">
-        <v>883600</v>
+        <v>877600</v>
       </c>
       <c r="H15" s="3">
-        <v>1241100</v>
+        <v>1232600</v>
       </c>
       <c r="I15" s="3">
-        <v>887300</v>
+        <v>881300</v>
       </c>
       <c r="J15" s="3">
-        <v>955600</v>
+        <v>949100</v>
       </c>
       <c r="K15" s="3">
         <v>956300</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2994800</v>
+        <v>2974400</v>
       </c>
       <c r="E17" s="3">
-        <v>3117200</v>
+        <v>3096000</v>
       </c>
       <c r="F17" s="3">
-        <v>2801200</v>
+        <v>2782200</v>
       </c>
       <c r="G17" s="3">
-        <v>3174700</v>
+        <v>3153200</v>
       </c>
       <c r="H17" s="3">
-        <v>3067000</v>
+        <v>3046200</v>
       </c>
       <c r="I17" s="3">
-        <v>3592100</v>
+        <v>3567700</v>
       </c>
       <c r="J17" s="3">
-        <v>3679100</v>
+        <v>3654100</v>
       </c>
       <c r="K17" s="3">
         <v>3802100</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>779700</v>
+        <v>774400</v>
       </c>
       <c r="E18" s="3">
-        <v>642500</v>
+        <v>638200</v>
       </c>
       <c r="F18" s="3">
-        <v>829000</v>
+        <v>823400</v>
       </c>
       <c r="G18" s="3">
-        <v>371300</v>
+        <v>368700</v>
       </c>
       <c r="H18" s="3">
-        <v>527000</v>
+        <v>523400</v>
       </c>
       <c r="I18" s="3">
-        <v>541200</v>
+        <v>537500</v>
       </c>
       <c r="J18" s="3">
-        <v>452300</v>
+        <v>449200</v>
       </c>
       <c r="K18" s="3">
         <v>438200</v>
@@ -1185,10 +1185,10 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-6000</v>
+        <v>4000</v>
       </c>
       <c r="E20" s="3">
-        <v>4700</v>
+        <v>4600</v>
       </c>
       <c r="F20" s="3">
         <v>2700</v>
@@ -1197,7 +1197,7 @@
         <v>-2100</v>
       </c>
       <c r="H20" s="3">
-        <v>19500</v>
+        <v>19300</v>
       </c>
       <c r="I20" s="3">
         <v>2300</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1503300</v>
+        <v>1494200</v>
       </c>
       <c r="E21" s="3">
-        <v>1517500</v>
+        <v>1496700</v>
       </c>
       <c r="F21" s="3">
-        <v>1562500</v>
+        <v>1543000</v>
       </c>
       <c r="G21" s="3">
-        <v>1281200</v>
+        <v>1261400</v>
       </c>
       <c r="H21" s="3">
-        <v>1868300</v>
+        <v>1839600</v>
       </c>
       <c r="I21" s="3">
-        <v>1370700</v>
+        <v>1351300</v>
       </c>
       <c r="J21" s="3">
-        <v>1367400</v>
+        <v>1347000</v>
       </c>
       <c r="K21" s="3">
         <v>1391900</v>
@@ -1275,25 +1275,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>12600</v>
+        <v>22500</v>
       </c>
       <c r="E22" s="3">
-        <v>43400</v>
+        <v>43100</v>
       </c>
       <c r="F22" s="3">
-        <v>49000</v>
+        <v>48600</v>
       </c>
       <c r="G22" s="3">
-        <v>61200</v>
+        <v>60700</v>
       </c>
       <c r="H22" s="3">
-        <v>101000</v>
+        <v>100300</v>
       </c>
       <c r="I22" s="3">
-        <v>93700</v>
+        <v>93000</v>
       </c>
       <c r="J22" s="3">
-        <v>151400</v>
+        <v>150300</v>
       </c>
       <c r="K22" s="3">
         <v>162100</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>761100</v>
+        <v>755900</v>
       </c>
       <c r="E23" s="3">
-        <v>603800</v>
+        <v>599700</v>
       </c>
       <c r="F23" s="3">
-        <v>782800</v>
+        <v>777500</v>
       </c>
       <c r="G23" s="3">
-        <v>308000</v>
+        <v>305900</v>
       </c>
       <c r="H23" s="3">
-        <v>445500</v>
+        <v>442400</v>
       </c>
       <c r="I23" s="3">
-        <v>449800</v>
+        <v>446800</v>
       </c>
       <c r="J23" s="3">
-        <v>296700</v>
+        <v>294700</v>
       </c>
       <c r="K23" s="3">
         <v>273900</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>182600</v>
+        <v>181300</v>
       </c>
       <c r="E24" s="3">
-        <v>180800</v>
+        <v>179600</v>
       </c>
       <c r="F24" s="3">
-        <v>254200</v>
+        <v>252500</v>
       </c>
       <c r="G24" s="3">
-        <v>49900</v>
+        <v>49600</v>
       </c>
       <c r="H24" s="3">
-        <v>100400</v>
+        <v>99700</v>
       </c>
       <c r="I24" s="3">
-        <v>180400</v>
+        <v>179200</v>
       </c>
       <c r="J24" s="3">
-        <v>160600</v>
+        <v>159500</v>
       </c>
       <c r="K24" s="3">
         <v>182700</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>578500</v>
+        <v>574600</v>
       </c>
       <c r="E26" s="3">
-        <v>422900</v>
+        <v>420100</v>
       </c>
       <c r="F26" s="3">
-        <v>528600</v>
+        <v>525000</v>
       </c>
       <c r="G26" s="3">
-        <v>258100</v>
+        <v>256300</v>
       </c>
       <c r="H26" s="3">
-        <v>345000</v>
+        <v>342700</v>
       </c>
       <c r="I26" s="3">
-        <v>269400</v>
+        <v>267600</v>
       </c>
       <c r="J26" s="3">
-        <v>136100</v>
+        <v>135200</v>
       </c>
       <c r="K26" s="3">
         <v>91100</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>578500</v>
+        <v>574600</v>
       </c>
       <c r="E27" s="3">
-        <v>422800</v>
+        <v>420000</v>
       </c>
       <c r="F27" s="3">
-        <v>493700</v>
+        <v>490300</v>
       </c>
       <c r="G27" s="3">
-        <v>240900</v>
+        <v>239300</v>
       </c>
       <c r="H27" s="3">
-        <v>521500</v>
+        <v>518000</v>
       </c>
       <c r="I27" s="3">
-        <v>279300</v>
+        <v>277400</v>
       </c>
       <c r="J27" s="3">
-        <v>184400</v>
+        <v>183200</v>
       </c>
       <c r="K27" s="3">
         <v>151900</v>
@@ -1596,19 +1596,19 @@
         <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>113100</v>
+        <v>112300</v>
       </c>
       <c r="G29" s="3">
-        <v>150700</v>
+        <v>149700</v>
       </c>
       <c r="H29" s="3">
-        <v>-298400</v>
+        <v>-296300</v>
       </c>
       <c r="I29" s="3">
-        <v>-88900</v>
+        <v>-88300</v>
       </c>
       <c r="J29" s="3">
-        <v>-111300</v>
+        <v>-110600</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1725,10 +1725,10 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>6000</v>
+        <v>-4000</v>
       </c>
       <c r="E32" s="3">
-        <v>-4700</v>
+        <v>-4600</v>
       </c>
       <c r="F32" s="3">
         <v>-2700</v>
@@ -1737,7 +1737,7 @@
         <v>2100</v>
       </c>
       <c r="H32" s="3">
-        <v>-19500</v>
+        <v>-19300</v>
       </c>
       <c r="I32" s="3">
         <v>-2300</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>578500</v>
+        <v>574600</v>
       </c>
       <c r="E33" s="3">
-        <v>422800</v>
+        <v>420000</v>
       </c>
       <c r="F33" s="3">
-        <v>606700</v>
+        <v>602600</v>
       </c>
       <c r="G33" s="3">
-        <v>391600</v>
+        <v>388900</v>
       </c>
       <c r="H33" s="3">
-        <v>223200</v>
+        <v>221700</v>
       </c>
       <c r="I33" s="3">
-        <v>190400</v>
+        <v>189100</v>
       </c>
       <c r="J33" s="3">
-        <v>73100</v>
+        <v>72600</v>
       </c>
       <c r="K33" s="3">
         <v>151900</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>578500</v>
+        <v>574600</v>
       </c>
       <c r="E35" s="3">
-        <v>422800</v>
+        <v>420000</v>
       </c>
       <c r="F35" s="3">
-        <v>606700</v>
+        <v>602600</v>
       </c>
       <c r="G35" s="3">
-        <v>391600</v>
+        <v>388900</v>
       </c>
       <c r="H35" s="3">
-        <v>223200</v>
+        <v>221700</v>
       </c>
       <c r="I35" s="3">
-        <v>190400</v>
+        <v>189100</v>
       </c>
       <c r="J35" s="3">
-        <v>73100</v>
+        <v>72600</v>
       </c>
       <c r="K35" s="3">
         <v>151900</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>504800</v>
+        <v>501300</v>
       </c>
       <c r="E41" s="3">
-        <v>642100</v>
+        <v>637700</v>
       </c>
       <c r="F41" s="3">
-        <v>686300</v>
+        <v>681600</v>
       </c>
       <c r="G41" s="3">
-        <v>561700</v>
+        <v>557900</v>
       </c>
       <c r="H41" s="3">
-        <v>1151500</v>
+        <v>1143700</v>
       </c>
       <c r="I41" s="3">
-        <v>1180300</v>
+        <v>1172200</v>
       </c>
       <c r="J41" s="3">
-        <v>1412000</v>
+        <v>1402400</v>
       </c>
       <c r="K41" s="3">
         <v>1720400</v>
@@ -2047,7 +2047,7 @@
         <v>6100</v>
       </c>
       <c r="G42" s="3">
-        <v>5900</v>
+        <v>5800</v>
       </c>
       <c r="H42" s="3">
         <v>6200</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>684200</v>
+        <v>679500</v>
       </c>
       <c r="E43" s="3">
-        <v>594200</v>
+        <v>590200</v>
       </c>
       <c r="F43" s="3">
-        <v>656000</v>
+        <v>651600</v>
       </c>
       <c r="G43" s="3">
-        <v>557900</v>
+        <v>554100</v>
       </c>
       <c r="H43" s="3">
-        <v>781700</v>
+        <v>776400</v>
       </c>
       <c r="I43" s="3">
-        <v>788700</v>
+        <v>783300</v>
       </c>
       <c r="J43" s="3">
-        <v>783100</v>
+        <v>777800</v>
       </c>
       <c r="K43" s="3">
         <v>792600</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>64100</v>
+        <v>63700</v>
       </c>
       <c r="E44" s="3">
-        <v>58800</v>
+        <v>58400</v>
       </c>
       <c r="F44" s="3">
-        <v>41300</v>
+        <v>41100</v>
       </c>
       <c r="G44" s="3">
-        <v>29300</v>
+        <v>29100</v>
       </c>
       <c r="H44" s="3">
-        <v>55800</v>
+        <v>55400</v>
       </c>
       <c r="I44" s="3">
-        <v>89200</v>
+        <v>88600</v>
       </c>
       <c r="J44" s="3">
-        <v>99300</v>
+        <v>98700</v>
       </c>
       <c r="K44" s="3">
         <v>104100</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>83800</v>
+        <v>83200</v>
       </c>
       <c r="E45" s="3">
-        <v>65900</v>
+        <v>65500</v>
       </c>
       <c r="F45" s="3">
-        <v>124900</v>
+        <v>124100</v>
       </c>
       <c r="G45" s="3">
-        <v>103600</v>
+        <v>102900</v>
       </c>
       <c r="H45" s="3">
-        <v>156000</v>
+        <v>155000</v>
       </c>
       <c r="I45" s="3">
-        <v>180600</v>
+        <v>179400</v>
       </c>
       <c r="J45" s="3">
-        <v>286800</v>
+        <v>284900</v>
       </c>
       <c r="K45" s="3">
         <v>337700</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1342900</v>
+        <v>1333800</v>
       </c>
       <c r="E46" s="3">
-        <v>1366200</v>
+        <v>1356900</v>
       </c>
       <c r="F46" s="3">
-        <v>1514600</v>
+        <v>1504300</v>
       </c>
       <c r="G46" s="3">
-        <v>1258300</v>
+        <v>1249700</v>
       </c>
       <c r="H46" s="3">
-        <v>2151300</v>
+        <v>2136700</v>
       </c>
       <c r="I46" s="3">
-        <v>2244300</v>
+        <v>2229100</v>
       </c>
       <c r="J46" s="3">
-        <v>2587700</v>
+        <v>2570100</v>
       </c>
       <c r="K46" s="3">
         <v>2960700</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>97400</v>
+        <v>96700</v>
       </c>
       <c r="E47" s="3">
-        <v>103400</v>
+        <v>102700</v>
       </c>
       <c r="F47" s="3">
-        <v>101300</v>
+        <v>100600</v>
       </c>
       <c r="G47" s="3">
-        <v>105800</v>
+        <v>105000</v>
       </c>
       <c r="H47" s="3">
-        <v>136100</v>
+        <v>135200</v>
       </c>
       <c r="I47" s="3">
-        <v>178300</v>
+        <v>177100</v>
       </c>
       <c r="J47" s="3">
-        <v>89900</v>
+        <v>89300</v>
       </c>
       <c r="K47" s="3">
         <v>93000</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2662300</v>
+        <v>2644100</v>
       </c>
       <c r="E48" s="3">
-        <v>2554500</v>
+        <v>2537200</v>
       </c>
       <c r="F48" s="3">
-        <v>2551600</v>
+        <v>2534200</v>
       </c>
       <c r="G48" s="3">
-        <v>2636100</v>
+        <v>2618200</v>
       </c>
       <c r="H48" s="3">
-        <v>3003000</v>
+        <v>2982600</v>
       </c>
       <c r="I48" s="3">
-        <v>2982600</v>
+        <v>2962300</v>
       </c>
       <c r="J48" s="3">
-        <v>2982400</v>
+        <v>2962100</v>
       </c>
       <c r="K48" s="3">
         <v>3095000</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>983300</v>
+        <v>976600</v>
       </c>
       <c r="E49" s="3">
-        <v>1096600</v>
+        <v>1089100</v>
       </c>
       <c r="F49" s="3">
-        <v>1211300</v>
+        <v>1203000</v>
       </c>
       <c r="G49" s="3">
-        <v>1246500</v>
+        <v>1238000</v>
       </c>
       <c r="H49" s="3">
-        <v>1227500</v>
+        <v>1219100</v>
       </c>
       <c r="I49" s="3">
-        <v>1444600</v>
+        <v>1434700</v>
       </c>
       <c r="J49" s="3">
-        <v>1604800</v>
+        <v>1593900</v>
       </c>
       <c r="K49" s="3">
         <v>1615200</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>285400</v>
+        <v>283500</v>
       </c>
       <c r="E52" s="3">
-        <v>275800</v>
+        <v>274000</v>
       </c>
       <c r="F52" s="3">
-        <v>297800</v>
+        <v>295800</v>
       </c>
       <c r="G52" s="3">
-        <v>1138200</v>
+        <v>1130400</v>
       </c>
       <c r="H52" s="3">
-        <v>398000</v>
+        <v>395300</v>
       </c>
       <c r="I52" s="3">
-        <v>440400</v>
+        <v>437400</v>
       </c>
       <c r="J52" s="3">
-        <v>463100</v>
+        <v>459900</v>
       </c>
       <c r="K52" s="3">
         <v>451300</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>5371300</v>
+        <v>5334800</v>
       </c>
       <c r="E54" s="3">
-        <v>5396500</v>
+        <v>5359800</v>
       </c>
       <c r="F54" s="3">
-        <v>5676600</v>
+        <v>5638000</v>
       </c>
       <c r="G54" s="3">
-        <v>6384900</v>
+        <v>6341400</v>
       </c>
       <c r="H54" s="3">
-        <v>6916000</v>
+        <v>6868900</v>
       </c>
       <c r="I54" s="3">
-        <v>7290200</v>
+        <v>7240600</v>
       </c>
       <c r="J54" s="3">
-        <v>7727900</v>
+        <v>7675300</v>
       </c>
       <c r="K54" s="3">
         <v>8215200</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>942700</v>
+        <v>936300</v>
       </c>
       <c r="E57" s="3">
-        <v>951000</v>
+        <v>944500</v>
       </c>
       <c r="F57" s="3">
-        <v>890600</v>
+        <v>884600</v>
       </c>
       <c r="G57" s="3">
-        <v>783200</v>
+        <v>777900</v>
       </c>
       <c r="H57" s="3">
-        <v>1018500</v>
+        <v>1011500</v>
       </c>
       <c r="I57" s="3">
-        <v>1125100</v>
+        <v>1117400</v>
       </c>
       <c r="J57" s="3">
-        <v>1264800</v>
+        <v>1256200</v>
       </c>
       <c r="K57" s="3">
         <v>1480000</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>66200</v>
+        <v>65700</v>
       </c>
       <c r="E58" s="3">
-        <v>271200</v>
+        <v>269300</v>
       </c>
       <c r="F58" s="3">
-        <v>510300</v>
+        <v>506800</v>
       </c>
       <c r="G58" s="3">
-        <v>315800</v>
+        <v>313600</v>
       </c>
       <c r="H58" s="3">
-        <v>848000</v>
+        <v>842200</v>
       </c>
       <c r="I58" s="3">
-        <v>596300</v>
+        <v>592200</v>
       </c>
       <c r="J58" s="3">
-        <v>831900</v>
+        <v>826200</v>
       </c>
       <c r="K58" s="3">
         <v>199700</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>785200</v>
+        <v>779800</v>
       </c>
       <c r="E59" s="3">
-        <v>701000</v>
+        <v>696200</v>
       </c>
       <c r="F59" s="3">
-        <v>707600</v>
+        <v>702800</v>
       </c>
       <c r="G59" s="3">
-        <v>809100</v>
+        <v>803600</v>
       </c>
       <c r="H59" s="3">
-        <v>765000</v>
+        <v>759800</v>
       </c>
       <c r="I59" s="3">
-        <v>820200</v>
+        <v>814600</v>
       </c>
       <c r="J59" s="3">
-        <v>864100</v>
+        <v>858200</v>
       </c>
       <c r="K59" s="3">
         <v>967800</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1794100</v>
+        <v>1781900</v>
       </c>
       <c r="E60" s="3">
-        <v>1923100</v>
+        <v>1910000</v>
       </c>
       <c r="F60" s="3">
-        <v>2108500</v>
+        <v>2094200</v>
       </c>
       <c r="G60" s="3">
-        <v>1908100</v>
+        <v>1895100</v>
       </c>
       <c r="H60" s="3">
-        <v>2631500</v>
+        <v>2613600</v>
       </c>
       <c r="I60" s="3">
-        <v>2541600</v>
+        <v>2524300</v>
       </c>
       <c r="J60" s="3">
-        <v>2960700</v>
+        <v>2940600</v>
       </c>
       <c r="K60" s="3">
         <v>2647600</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1123600</v>
+        <v>1115900</v>
       </c>
       <c r="E61" s="3">
-        <v>1157300</v>
+        <v>1149400</v>
       </c>
       <c r="F61" s="3">
-        <v>1026000</v>
+        <v>1019000</v>
       </c>
       <c r="G61" s="3">
-        <v>1376900</v>
+        <v>1367500</v>
       </c>
       <c r="H61" s="3">
-        <v>1448200</v>
+        <v>1438300</v>
       </c>
       <c r="I61" s="3">
-        <v>1393400</v>
+        <v>1383900</v>
       </c>
       <c r="J61" s="3">
-        <v>1388600</v>
+        <v>1379200</v>
       </c>
       <c r="K61" s="3">
         <v>2106000</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>338600</v>
+        <v>336300</v>
       </c>
       <c r="E62" s="3">
-        <v>304300</v>
+        <v>302300</v>
       </c>
       <c r="F62" s="3">
-        <v>396200</v>
+        <v>393500</v>
       </c>
       <c r="G62" s="3">
-        <v>433000</v>
+        <v>430000</v>
       </c>
       <c r="H62" s="3">
-        <v>460900</v>
+        <v>457800</v>
       </c>
       <c r="I62" s="3">
-        <v>511500</v>
+        <v>508000</v>
       </c>
       <c r="J62" s="3">
-        <v>561000</v>
+        <v>557200</v>
       </c>
       <c r="K62" s="3">
         <v>584500</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>3256800</v>
+        <v>3234600</v>
       </c>
       <c r="E66" s="3">
-        <v>3385300</v>
+        <v>3362300</v>
       </c>
       <c r="F66" s="3">
-        <v>3532500</v>
+        <v>3508500</v>
       </c>
       <c r="G66" s="3">
-        <v>4213200</v>
+        <v>4184600</v>
       </c>
       <c r="H66" s="3">
-        <v>4683200</v>
+        <v>4651300</v>
       </c>
       <c r="I66" s="3">
-        <v>4751400</v>
+        <v>4719100</v>
       </c>
       <c r="J66" s="3">
-        <v>5177000</v>
+        <v>5141800</v>
       </c>
       <c r="K66" s="3">
         <v>5658900</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>541100</v>
+        <v>537400</v>
       </c>
       <c r="E72" s="3">
-        <v>423800</v>
+        <v>420900</v>
       </c>
       <c r="F72" s="3">
-        <v>4156100</v>
+        <v>4127800</v>
       </c>
       <c r="G72" s="3">
-        <v>4142300</v>
+        <v>4114100</v>
       </c>
       <c r="H72" s="3">
-        <v>4106100</v>
+        <v>4078100</v>
       </c>
       <c r="I72" s="3">
-        <v>4333200</v>
+        <v>4303800</v>
       </c>
       <c r="J72" s="3">
-        <v>4123400</v>
+        <v>4095300</v>
       </c>
       <c r="K72" s="3">
         <v>4124200</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2114500</v>
+        <v>2100100</v>
       </c>
       <c r="E76" s="3">
-        <v>2011200</v>
+        <v>1997600</v>
       </c>
       <c r="F76" s="3">
-        <v>2144100</v>
+        <v>2129500</v>
       </c>
       <c r="G76" s="3">
-        <v>2171600</v>
+        <v>2156900</v>
       </c>
       <c r="H76" s="3">
-        <v>2232800</v>
+        <v>2217600</v>
       </c>
       <c r="I76" s="3">
-        <v>2538800</v>
+        <v>2521500</v>
       </c>
       <c r="J76" s="3">
-        <v>2550900</v>
+        <v>2533600</v>
       </c>
       <c r="K76" s="3">
         <v>2556300</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>578500</v>
+        <v>574600</v>
       </c>
       <c r="E81" s="3">
-        <v>422800</v>
+        <v>420000</v>
       </c>
       <c r="F81" s="3">
-        <v>606700</v>
+        <v>602600</v>
       </c>
       <c r="G81" s="3">
-        <v>391600</v>
+        <v>388900</v>
       </c>
       <c r="H81" s="3">
-        <v>223200</v>
+        <v>221700</v>
       </c>
       <c r="I81" s="3">
-        <v>190400</v>
+        <v>189100</v>
       </c>
       <c r="J81" s="3">
-        <v>73100</v>
+        <v>72600</v>
       </c>
       <c r="K81" s="3">
         <v>151900</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>725200</v>
+        <v>720300</v>
       </c>
       <c r="E83" s="3">
-        <v>865100</v>
+        <v>859300</v>
       </c>
       <c r="F83" s="3">
-        <v>726400</v>
+        <v>721500</v>
       </c>
       <c r="G83" s="3">
-        <v>906600</v>
+        <v>900400</v>
       </c>
       <c r="H83" s="3">
-        <v>1314000</v>
+        <v>1305100</v>
       </c>
       <c r="I83" s="3">
-        <v>822300</v>
+        <v>816700</v>
       </c>
       <c r="J83" s="3">
-        <v>913900</v>
+        <v>907700</v>
       </c>
       <c r="K83" s="3">
         <v>956300</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1300400</v>
+        <v>1291500</v>
       </c>
       <c r="E89" s="3">
-        <v>1433200</v>
+        <v>1423500</v>
       </c>
       <c r="F89" s="3">
-        <v>1411800</v>
+        <v>1402200</v>
       </c>
       <c r="G89" s="3">
-        <v>1278100</v>
+        <v>1269400</v>
       </c>
       <c r="H89" s="3">
-        <v>1262500</v>
+        <v>1253900</v>
       </c>
       <c r="I89" s="3">
-        <v>1075000</v>
+        <v>1067700</v>
       </c>
       <c r="J89" s="3">
-        <v>871100</v>
+        <v>865200</v>
       </c>
       <c r="K89" s="3">
         <v>1112200</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-676100</v>
+        <v>-671500</v>
       </c>
       <c r="E91" s="3">
-        <v>-695800</v>
+        <v>-691100</v>
       </c>
       <c r="F91" s="3">
-        <v>-637600</v>
+        <v>-633300</v>
       </c>
       <c r="G91" s="3">
-        <v>-726600</v>
+        <v>-721700</v>
       </c>
       <c r="H91" s="3">
-        <v>-720100</v>
+        <v>-715200</v>
       </c>
       <c r="I91" s="3">
-        <v>-783300</v>
+        <v>-778000</v>
       </c>
       <c r="J91" s="3">
-        <v>-983900</v>
+        <v>-977200</v>
       </c>
       <c r="K91" s="3">
         <v>-708500</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-658100</v>
+        <v>-653600</v>
       </c>
       <c r="E94" s="3">
-        <v>-694800</v>
+        <v>-690000</v>
       </c>
       <c r="F94" s="3">
-        <v>-473900</v>
+        <v>-470600</v>
       </c>
       <c r="G94" s="3">
-        <v>-794400</v>
+        <v>-789000</v>
       </c>
       <c r="H94" s="3">
-        <v>-686200</v>
+        <v>-681500</v>
       </c>
       <c r="I94" s="3">
-        <v>-784800</v>
+        <v>-779500</v>
       </c>
       <c r="J94" s="3">
-        <v>-993100</v>
+        <v>-986400</v>
       </c>
       <c r="K94" s="3">
         <v>-702000</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-271900</v>
+        <v>-270100</v>
       </c>
       <c r="E96" s="3">
-        <v>-271900</v>
+        <v>-270100</v>
       </c>
       <c r="F96" s="3">
-        <v>-463600</v>
+        <v>-460500</v>
       </c>
       <c r="G96" s="3">
-        <v>-280600</v>
+        <v>-278700</v>
       </c>
       <c r="H96" s="3">
-        <v>-270900</v>
+        <v>-269100</v>
       </c>
       <c r="I96" s="3">
-        <v>-186200</v>
+        <v>-184900</v>
       </c>
       <c r="J96" s="3">
-        <v>-85000</v>
+        <v>-84400</v>
       </c>
       <c r="K96" s="3">
         <v>-53100</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-779400</v>
+        <v>-774100</v>
       </c>
       <c r="E100" s="3">
-        <v>-785000</v>
+        <v>-779600</v>
       </c>
       <c r="F100" s="3">
-        <v>-812300</v>
+        <v>-806700</v>
       </c>
       <c r="G100" s="3">
-        <v>-1070500</v>
+        <v>-1063200</v>
       </c>
       <c r="H100" s="3">
-        <v>-602900</v>
+        <v>-598800</v>
       </c>
       <c r="I100" s="3">
-        <v>-522300</v>
+        <v>-518700</v>
       </c>
       <c r="J100" s="3">
-        <v>-186200</v>
+        <v>-184900</v>
       </c>
       <c r="K100" s="3">
         <v>-124100</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-137300</v>
+        <v>-136400</v>
       </c>
       <c r="E102" s="3">
-        <v>-44200</v>
+        <v>-43900</v>
       </c>
       <c r="F102" s="3">
-        <v>124600</v>
+        <v>123700</v>
       </c>
       <c r="G102" s="3">
-        <v>-589900</v>
+        <v>-585800</v>
       </c>
       <c r="H102" s="3">
-        <v>-28700</v>
+        <v>-28500</v>
       </c>
       <c r="I102" s="3">
-        <v>-231800</v>
+        <v>-230200</v>
       </c>
       <c r="J102" s="3">
-        <v>-313300</v>
+        <v>-311100</v>
       </c>
       <c r="K102" s="3">
         <v>285500</v>

--- a/AAII_Financials/Yearly/HLTOY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HLTOY_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>3748800</v>
+        <v>3842200</v>
       </c>
       <c r="E8" s="3">
-        <v>3734100</v>
+        <v>3827100</v>
       </c>
       <c r="F8" s="3">
-        <v>3605500</v>
+        <v>3695300</v>
       </c>
       <c r="G8" s="3">
-        <v>3521900</v>
+        <v>3609600</v>
       </c>
       <c r="H8" s="3">
-        <v>3569600</v>
+        <v>3658400</v>
       </c>
       <c r="I8" s="3">
-        <v>4105300</v>
+        <v>4207400</v>
       </c>
       <c r="J8" s="3">
-        <v>4103300</v>
+        <v>4205400</v>
       </c>
       <c r="K8" s="3">
         <v>4240300</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>350400</v>
+        <v>359100</v>
       </c>
       <c r="E9" s="3">
-        <v>236800</v>
+        <v>242700</v>
       </c>
       <c r="F9" s="3">
-        <v>186300</v>
+        <v>191000</v>
       </c>
       <c r="G9" s="3">
-        <v>177800</v>
+        <v>182200</v>
       </c>
       <c r="H9" s="3">
-        <v>151200</v>
+        <v>155000</v>
       </c>
       <c r="I9" s="3">
-        <v>162800</v>
+        <v>166800</v>
       </c>
       <c r="J9" s="3">
-        <v>176700</v>
+        <v>181100</v>
       </c>
       <c r="K9" s="3">
         <v>194100</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>3398500</v>
+        <v>3483100</v>
       </c>
       <c r="E10" s="3">
-        <v>3497400</v>
+        <v>3584400</v>
       </c>
       <c r="F10" s="3">
-        <v>3419200</v>
+        <v>3504300</v>
       </c>
       <c r="G10" s="3">
-        <v>3344100</v>
+        <v>3427400</v>
       </c>
       <c r="H10" s="3">
-        <v>3418400</v>
+        <v>3503400</v>
       </c>
       <c r="I10" s="3">
-        <v>3942500</v>
+        <v>4040600</v>
       </c>
       <c r="J10" s="3">
-        <v>3926600</v>
+        <v>4024400</v>
       </c>
       <c r="K10" s="3">
         <v>4046200</v>
@@ -976,19 +976,19 @@
         <v>0</v>
       </c>
       <c r="F14" s="3">
-        <v>54500</v>
+        <v>55800</v>
       </c>
       <c r="G14" s="3">
-        <v>-10600</v>
+        <v>-10900</v>
       </c>
       <c r="H14" s="3">
-        <v>45200</v>
+        <v>46300</v>
       </c>
       <c r="I14" s="3">
         <v>-2400</v>
       </c>
       <c r="J14" s="3">
-        <v>43000</v>
+        <v>44100</v>
       </c>
       <c r="K14" s="3">
         <v>-19900</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>720300</v>
+        <v>738200</v>
       </c>
       <c r="E15" s="3">
-        <v>859300</v>
+        <v>880700</v>
       </c>
       <c r="F15" s="3">
-        <v>721500</v>
+        <v>739400</v>
       </c>
       <c r="G15" s="3">
-        <v>877600</v>
+        <v>899500</v>
       </c>
       <c r="H15" s="3">
-        <v>1232600</v>
+        <v>1263300</v>
       </c>
       <c r="I15" s="3">
-        <v>881300</v>
+        <v>903200</v>
       </c>
       <c r="J15" s="3">
-        <v>949100</v>
+        <v>972700</v>
       </c>
       <c r="K15" s="3">
         <v>956300</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2974400</v>
+        <v>3048400</v>
       </c>
       <c r="E17" s="3">
-        <v>3096000</v>
+        <v>3173100</v>
       </c>
       <c r="F17" s="3">
-        <v>2782200</v>
+        <v>2851400</v>
       </c>
       <c r="G17" s="3">
-        <v>3153200</v>
+        <v>3231600</v>
       </c>
       <c r="H17" s="3">
-        <v>3046200</v>
+        <v>3122000</v>
       </c>
       <c r="I17" s="3">
-        <v>3567700</v>
+        <v>3656500</v>
       </c>
       <c r="J17" s="3">
-        <v>3654100</v>
+        <v>3745000</v>
       </c>
       <c r="K17" s="3">
         <v>3802100</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>774400</v>
+        <v>793700</v>
       </c>
       <c r="E18" s="3">
-        <v>638200</v>
+        <v>654000</v>
       </c>
       <c r="F18" s="3">
-        <v>823400</v>
+        <v>843900</v>
       </c>
       <c r="G18" s="3">
-        <v>368700</v>
+        <v>377900</v>
       </c>
       <c r="H18" s="3">
-        <v>523400</v>
+        <v>536400</v>
       </c>
       <c r="I18" s="3">
-        <v>537500</v>
+        <v>550900</v>
       </c>
       <c r="J18" s="3">
-        <v>449200</v>
+        <v>460400</v>
       </c>
       <c r="K18" s="3">
         <v>438200</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="E20" s="3">
-        <v>4600</v>
+        <v>4800</v>
       </c>
       <c r="F20" s="3">
-        <v>2700</v>
+        <v>2800</v>
       </c>
       <c r="G20" s="3">
         <v>-2100</v>
       </c>
       <c r="H20" s="3">
-        <v>19300</v>
+        <v>19800</v>
       </c>
       <c r="I20" s="3">
         <v>2300</v>
       </c>
       <c r="J20" s="3">
-        <v>-4200</v>
+        <v>-4300</v>
       </c>
       <c r="K20" s="3">
         <v>-2300</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1494200</v>
+        <v>1535900</v>
       </c>
       <c r="E21" s="3">
-        <v>1496700</v>
+        <v>1539300</v>
       </c>
       <c r="F21" s="3">
-        <v>1543000</v>
+        <v>1585900</v>
       </c>
       <c r="G21" s="3">
-        <v>1261400</v>
+        <v>1298500</v>
       </c>
       <c r="H21" s="3">
-        <v>1839600</v>
+        <v>1893500</v>
       </c>
       <c r="I21" s="3">
-        <v>1351300</v>
+        <v>1390100</v>
       </c>
       <c r="J21" s="3">
-        <v>1347000</v>
+        <v>1386200</v>
       </c>
       <c r="K21" s="3">
         <v>1391900</v>
@@ -1275,25 +1275,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>22500</v>
+        <v>23000</v>
       </c>
       <c r="E22" s="3">
-        <v>43100</v>
+        <v>44200</v>
       </c>
       <c r="F22" s="3">
-        <v>48600</v>
+        <v>49800</v>
       </c>
       <c r="G22" s="3">
-        <v>60700</v>
+        <v>62200</v>
       </c>
       <c r="H22" s="3">
-        <v>100300</v>
+        <v>102800</v>
       </c>
       <c r="I22" s="3">
-        <v>93000</v>
+        <v>95400</v>
       </c>
       <c r="J22" s="3">
-        <v>150300</v>
+        <v>154100</v>
       </c>
       <c r="K22" s="3">
         <v>162100</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>755900</v>
+        <v>774800</v>
       </c>
       <c r="E23" s="3">
-        <v>599700</v>
+        <v>614600</v>
       </c>
       <c r="F23" s="3">
-        <v>777500</v>
+        <v>796800</v>
       </c>
       <c r="G23" s="3">
-        <v>305900</v>
+        <v>313600</v>
       </c>
       <c r="H23" s="3">
-        <v>442400</v>
+        <v>453500</v>
       </c>
       <c r="I23" s="3">
-        <v>446800</v>
+        <v>457900</v>
       </c>
       <c r="J23" s="3">
-        <v>294700</v>
+        <v>302000</v>
       </c>
       <c r="K23" s="3">
         <v>273900</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>181300</v>
+        <v>185900</v>
       </c>
       <c r="E24" s="3">
-        <v>179600</v>
+        <v>184100</v>
       </c>
       <c r="F24" s="3">
-        <v>252500</v>
+        <v>258700</v>
       </c>
       <c r="G24" s="3">
-        <v>49600</v>
+        <v>50800</v>
       </c>
       <c r="H24" s="3">
-        <v>99700</v>
+        <v>102200</v>
       </c>
       <c r="I24" s="3">
-        <v>179200</v>
+        <v>183600</v>
       </c>
       <c r="J24" s="3">
-        <v>159500</v>
+        <v>163500</v>
       </c>
       <c r="K24" s="3">
         <v>182700</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>574600</v>
+        <v>588900</v>
       </c>
       <c r="E26" s="3">
-        <v>420100</v>
+        <v>430500</v>
       </c>
       <c r="F26" s="3">
-        <v>525000</v>
+        <v>538100</v>
       </c>
       <c r="G26" s="3">
-        <v>256300</v>
+        <v>262700</v>
       </c>
       <c r="H26" s="3">
-        <v>342700</v>
+        <v>351200</v>
       </c>
       <c r="I26" s="3">
-        <v>267600</v>
+        <v>274200</v>
       </c>
       <c r="J26" s="3">
-        <v>135200</v>
+        <v>138600</v>
       </c>
       <c r="K26" s="3">
         <v>91100</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>574600</v>
+        <v>588900</v>
       </c>
       <c r="E27" s="3">
-        <v>420000</v>
+        <v>430400</v>
       </c>
       <c r="F27" s="3">
-        <v>490300</v>
+        <v>502500</v>
       </c>
       <c r="G27" s="3">
-        <v>239300</v>
+        <v>245200</v>
       </c>
       <c r="H27" s="3">
-        <v>518000</v>
+        <v>530900</v>
       </c>
       <c r="I27" s="3">
-        <v>277400</v>
+        <v>284300</v>
       </c>
       <c r="J27" s="3">
-        <v>183200</v>
+        <v>187700</v>
       </c>
       <c r="K27" s="3">
         <v>151900</v>
@@ -1596,19 +1596,19 @@
         <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>112300</v>
+        <v>115100</v>
       </c>
       <c r="G29" s="3">
-        <v>149700</v>
+        <v>153400</v>
       </c>
       <c r="H29" s="3">
-        <v>-296300</v>
+        <v>-303700</v>
       </c>
       <c r="I29" s="3">
-        <v>-88300</v>
+        <v>-90500</v>
       </c>
       <c r="J29" s="3">
-        <v>-110600</v>
+        <v>-113300</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-4000</v>
+        <v>-4100</v>
       </c>
       <c r="E32" s="3">
-        <v>-4600</v>
+        <v>-4800</v>
       </c>
       <c r="F32" s="3">
-        <v>-2700</v>
+        <v>-2800</v>
       </c>
       <c r="G32" s="3">
         <v>2100</v>
       </c>
       <c r="H32" s="3">
-        <v>-19300</v>
+        <v>-19800</v>
       </c>
       <c r="I32" s="3">
         <v>-2300</v>
       </c>
       <c r="J32" s="3">
-        <v>4200</v>
+        <v>4300</v>
       </c>
       <c r="K32" s="3">
         <v>2300</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>574600</v>
+        <v>588900</v>
       </c>
       <c r="E33" s="3">
-        <v>420000</v>
+        <v>430400</v>
       </c>
       <c r="F33" s="3">
-        <v>602600</v>
+        <v>617600</v>
       </c>
       <c r="G33" s="3">
-        <v>388900</v>
+        <v>398600</v>
       </c>
       <c r="H33" s="3">
-        <v>221700</v>
+        <v>227200</v>
       </c>
       <c r="I33" s="3">
-        <v>189100</v>
+        <v>193800</v>
       </c>
       <c r="J33" s="3">
-        <v>72600</v>
+        <v>74400</v>
       </c>
       <c r="K33" s="3">
         <v>151900</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>574600</v>
+        <v>588900</v>
       </c>
       <c r="E35" s="3">
-        <v>420000</v>
+        <v>430400</v>
       </c>
       <c r="F35" s="3">
-        <v>602600</v>
+        <v>617600</v>
       </c>
       <c r="G35" s="3">
-        <v>388900</v>
+        <v>398600</v>
       </c>
       <c r="H35" s="3">
-        <v>221700</v>
+        <v>227200</v>
       </c>
       <c r="I35" s="3">
-        <v>189100</v>
+        <v>193800</v>
       </c>
       <c r="J35" s="3">
-        <v>72600</v>
+        <v>74400</v>
       </c>
       <c r="K35" s="3">
         <v>151900</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>501300</v>
+        <v>513800</v>
       </c>
       <c r="E41" s="3">
-        <v>637700</v>
+        <v>653600</v>
       </c>
       <c r="F41" s="3">
-        <v>681600</v>
+        <v>698600</v>
       </c>
       <c r="G41" s="3">
-        <v>557900</v>
+        <v>571700</v>
       </c>
       <c r="H41" s="3">
-        <v>1143700</v>
+        <v>1172200</v>
       </c>
       <c r="I41" s="3">
-        <v>1172200</v>
+        <v>1201400</v>
       </c>
       <c r="J41" s="3">
-        <v>1402400</v>
+        <v>1437300</v>
       </c>
       <c r="K41" s="3">
         <v>1720400</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>6100</v>
+        <v>6200</v>
       </c>
       <c r="E42" s="3">
-        <v>5200</v>
+        <v>5300</v>
       </c>
       <c r="F42" s="3">
-        <v>6100</v>
+        <v>6200</v>
       </c>
       <c r="G42" s="3">
-        <v>5800</v>
+        <v>6000</v>
       </c>
       <c r="H42" s="3">
-        <v>6200</v>
+        <v>6300</v>
       </c>
       <c r="I42" s="3">
-        <v>5500</v>
+        <v>5600</v>
       </c>
       <c r="J42" s="3">
-        <v>6400</v>
+        <v>6500</v>
       </c>
       <c r="K42" s="3">
         <v>6100</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>679500</v>
+        <v>696500</v>
       </c>
       <c r="E43" s="3">
-        <v>590200</v>
+        <v>604900</v>
       </c>
       <c r="F43" s="3">
-        <v>651600</v>
+        <v>667800</v>
       </c>
       <c r="G43" s="3">
-        <v>554100</v>
+        <v>567900</v>
       </c>
       <c r="H43" s="3">
-        <v>776400</v>
+        <v>795700</v>
       </c>
       <c r="I43" s="3">
-        <v>783300</v>
+        <v>802800</v>
       </c>
       <c r="J43" s="3">
-        <v>777800</v>
+        <v>797100</v>
       </c>
       <c r="K43" s="3">
         <v>792600</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>63700</v>
+        <v>65200</v>
       </c>
       <c r="E44" s="3">
-        <v>58400</v>
+        <v>59800</v>
       </c>
       <c r="F44" s="3">
-        <v>41100</v>
+        <v>42100</v>
       </c>
       <c r="G44" s="3">
-        <v>29100</v>
+        <v>29800</v>
       </c>
       <c r="H44" s="3">
-        <v>55400</v>
+        <v>56800</v>
       </c>
       <c r="I44" s="3">
-        <v>88600</v>
+        <v>90800</v>
       </c>
       <c r="J44" s="3">
-        <v>98700</v>
+        <v>101100</v>
       </c>
       <c r="K44" s="3">
         <v>104100</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>83200</v>
+        <v>85300</v>
       </c>
       <c r="E45" s="3">
-        <v>65500</v>
+        <v>67100</v>
       </c>
       <c r="F45" s="3">
-        <v>124100</v>
+        <v>127200</v>
       </c>
       <c r="G45" s="3">
-        <v>102900</v>
+        <v>105400</v>
       </c>
       <c r="H45" s="3">
-        <v>155000</v>
+        <v>158800</v>
       </c>
       <c r="I45" s="3">
-        <v>179400</v>
+        <v>183900</v>
       </c>
       <c r="J45" s="3">
-        <v>284900</v>
+        <v>292000</v>
       </c>
       <c r="K45" s="3">
         <v>337700</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1333800</v>
+        <v>1367000</v>
       </c>
       <c r="E46" s="3">
-        <v>1356900</v>
+        <v>1390700</v>
       </c>
       <c r="F46" s="3">
-        <v>1504300</v>
+        <v>1541800</v>
       </c>
       <c r="G46" s="3">
-        <v>1249700</v>
+        <v>1280800</v>
       </c>
       <c r="H46" s="3">
-        <v>2136700</v>
+        <v>2189800</v>
       </c>
       <c r="I46" s="3">
-        <v>2229100</v>
+        <v>2284500</v>
       </c>
       <c r="J46" s="3">
-        <v>2570100</v>
+        <v>2634100</v>
       </c>
       <c r="K46" s="3">
         <v>2960700</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>96700</v>
+        <v>99100</v>
       </c>
       <c r="E47" s="3">
-        <v>102700</v>
+        <v>105200</v>
       </c>
       <c r="F47" s="3">
-        <v>100600</v>
+        <v>103100</v>
       </c>
       <c r="G47" s="3">
-        <v>105000</v>
+        <v>107700</v>
       </c>
       <c r="H47" s="3">
-        <v>135200</v>
+        <v>138600</v>
       </c>
       <c r="I47" s="3">
-        <v>177100</v>
+        <v>181500</v>
       </c>
       <c r="J47" s="3">
-        <v>89300</v>
+        <v>91500</v>
       </c>
       <c r="K47" s="3">
         <v>93000</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2644100</v>
+        <v>2710000</v>
       </c>
       <c r="E48" s="3">
-        <v>2537200</v>
+        <v>2600300</v>
       </c>
       <c r="F48" s="3">
-        <v>2534200</v>
+        <v>2597300</v>
       </c>
       <c r="G48" s="3">
-        <v>2618200</v>
+        <v>2683400</v>
       </c>
       <c r="H48" s="3">
-        <v>2982600</v>
+        <v>3056900</v>
       </c>
       <c r="I48" s="3">
-        <v>2962300</v>
+        <v>3036000</v>
       </c>
       <c r="J48" s="3">
-        <v>2962100</v>
+        <v>3035800</v>
       </c>
       <c r="K48" s="3">
         <v>3095000</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>976600</v>
+        <v>1000900</v>
       </c>
       <c r="E49" s="3">
-        <v>1089100</v>
+        <v>1116200</v>
       </c>
       <c r="F49" s="3">
-        <v>1203000</v>
+        <v>1233000</v>
       </c>
       <c r="G49" s="3">
-        <v>1238000</v>
+        <v>1268900</v>
       </c>
       <c r="H49" s="3">
-        <v>1219100</v>
+        <v>1249500</v>
       </c>
       <c r="I49" s="3">
-        <v>1434700</v>
+        <v>1470400</v>
       </c>
       <c r="J49" s="3">
-        <v>1593900</v>
+        <v>1633600</v>
       </c>
       <c r="K49" s="3">
         <v>1615200</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>283500</v>
+        <v>290500</v>
       </c>
       <c r="E52" s="3">
-        <v>274000</v>
+        <v>280800</v>
       </c>
       <c r="F52" s="3">
-        <v>295800</v>
+        <v>303200</v>
       </c>
       <c r="G52" s="3">
-        <v>1130400</v>
+        <v>1158500</v>
       </c>
       <c r="H52" s="3">
-        <v>395300</v>
+        <v>405200</v>
       </c>
       <c r="I52" s="3">
-        <v>437400</v>
+        <v>448200</v>
       </c>
       <c r="J52" s="3">
-        <v>459900</v>
+        <v>471400</v>
       </c>
       <c r="K52" s="3">
         <v>451300</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>5334800</v>
+        <v>5467600</v>
       </c>
       <c r="E54" s="3">
-        <v>5359800</v>
+        <v>5493300</v>
       </c>
       <c r="F54" s="3">
-        <v>5638000</v>
+        <v>5778300</v>
       </c>
       <c r="G54" s="3">
-        <v>6341400</v>
+        <v>6499300</v>
       </c>
       <c r="H54" s="3">
-        <v>6868900</v>
+        <v>7039900</v>
       </c>
       <c r="I54" s="3">
-        <v>7240600</v>
+        <v>7420800</v>
       </c>
       <c r="J54" s="3">
-        <v>7675300</v>
+        <v>7866400</v>
       </c>
       <c r="K54" s="3">
         <v>8215200</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>936300</v>
+        <v>959600</v>
       </c>
       <c r="E57" s="3">
-        <v>944500</v>
+        <v>968000</v>
       </c>
       <c r="F57" s="3">
-        <v>884600</v>
+        <v>906600</v>
       </c>
       <c r="G57" s="3">
-        <v>777900</v>
+        <v>797300</v>
       </c>
       <c r="H57" s="3">
-        <v>1011500</v>
+        <v>1036700</v>
       </c>
       <c r="I57" s="3">
-        <v>1117400</v>
+        <v>1145300</v>
       </c>
       <c r="J57" s="3">
-        <v>1256200</v>
+        <v>1287500</v>
       </c>
       <c r="K57" s="3">
         <v>1480000</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>65700</v>
+        <v>67300</v>
       </c>
       <c r="E58" s="3">
-        <v>269300</v>
+        <v>276000</v>
       </c>
       <c r="F58" s="3">
-        <v>506800</v>
+        <v>519500</v>
       </c>
       <c r="G58" s="3">
-        <v>313600</v>
+        <v>321400</v>
       </c>
       <c r="H58" s="3">
-        <v>842200</v>
+        <v>863200</v>
       </c>
       <c r="I58" s="3">
-        <v>592200</v>
+        <v>607000</v>
       </c>
       <c r="J58" s="3">
-        <v>826200</v>
+        <v>846800</v>
       </c>
       <c r="K58" s="3">
         <v>199700</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>779800</v>
+        <v>799200</v>
       </c>
       <c r="E59" s="3">
-        <v>696200</v>
+        <v>713500</v>
       </c>
       <c r="F59" s="3">
-        <v>702800</v>
+        <v>720300</v>
       </c>
       <c r="G59" s="3">
-        <v>803600</v>
+        <v>823600</v>
       </c>
       <c r="H59" s="3">
-        <v>759800</v>
+        <v>778800</v>
       </c>
       <c r="I59" s="3">
-        <v>814600</v>
+        <v>834900</v>
       </c>
       <c r="J59" s="3">
-        <v>858200</v>
+        <v>879500</v>
       </c>
       <c r="K59" s="3">
         <v>967800</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1781900</v>
+        <v>1826200</v>
       </c>
       <c r="E60" s="3">
-        <v>1910000</v>
+        <v>1957600</v>
       </c>
       <c r="F60" s="3">
-        <v>2094200</v>
+        <v>2146300</v>
       </c>
       <c r="G60" s="3">
-        <v>1895100</v>
+        <v>1942300</v>
       </c>
       <c r="H60" s="3">
-        <v>2613600</v>
+        <v>2678600</v>
       </c>
       <c r="I60" s="3">
-        <v>2524300</v>
+        <v>2587100</v>
       </c>
       <c r="J60" s="3">
-        <v>2940600</v>
+        <v>3013800</v>
       </c>
       <c r="K60" s="3">
         <v>2647600</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1115900</v>
+        <v>1143700</v>
       </c>
       <c r="E61" s="3">
-        <v>1149400</v>
+        <v>1178000</v>
       </c>
       <c r="F61" s="3">
-        <v>1019000</v>
+        <v>1044400</v>
       </c>
       <c r="G61" s="3">
-        <v>1367500</v>
+        <v>1401600</v>
       </c>
       <c r="H61" s="3">
-        <v>1438300</v>
+        <v>1474100</v>
       </c>
       <c r="I61" s="3">
-        <v>1383900</v>
+        <v>1418400</v>
       </c>
       <c r="J61" s="3">
-        <v>1379200</v>
+        <v>1413500</v>
       </c>
       <c r="K61" s="3">
         <v>2106000</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>336300</v>
+        <v>344700</v>
       </c>
       <c r="E62" s="3">
-        <v>302300</v>
+        <v>309800</v>
       </c>
       <c r="F62" s="3">
-        <v>393500</v>
+        <v>403300</v>
       </c>
       <c r="G62" s="3">
-        <v>430000</v>
+        <v>440700</v>
       </c>
       <c r="H62" s="3">
-        <v>457800</v>
+        <v>469200</v>
       </c>
       <c r="I62" s="3">
-        <v>508000</v>
+        <v>520700</v>
       </c>
       <c r="J62" s="3">
-        <v>557200</v>
+        <v>571100</v>
       </c>
       <c r="K62" s="3">
         <v>584500</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>3234600</v>
+        <v>3315200</v>
       </c>
       <c r="E66" s="3">
-        <v>3362300</v>
+        <v>3446000</v>
       </c>
       <c r="F66" s="3">
-        <v>3508500</v>
+        <v>3595800</v>
       </c>
       <c r="G66" s="3">
-        <v>4184600</v>
+        <v>4288700</v>
       </c>
       <c r="H66" s="3">
-        <v>4651300</v>
+        <v>4767100</v>
       </c>
       <c r="I66" s="3">
-        <v>4719100</v>
+        <v>4836600</v>
       </c>
       <c r="J66" s="3">
-        <v>5141800</v>
+        <v>5269700</v>
       </c>
       <c r="K66" s="3">
         <v>5658900</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>537400</v>
+        <v>550800</v>
       </c>
       <c r="E72" s="3">
-        <v>420900</v>
+        <v>431400</v>
       </c>
       <c r="F72" s="3">
-        <v>4127800</v>
+        <v>4230600</v>
       </c>
       <c r="G72" s="3">
-        <v>4114100</v>
+        <v>4216500</v>
       </c>
       <c r="H72" s="3">
-        <v>4078100</v>
+        <v>4179600</v>
       </c>
       <c r="I72" s="3">
-        <v>4303800</v>
+        <v>4410900</v>
       </c>
       <c r="J72" s="3">
-        <v>4095300</v>
+        <v>4197300</v>
       </c>
       <c r="K72" s="3">
         <v>4124200</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2100100</v>
+        <v>2152400</v>
       </c>
       <c r="E76" s="3">
-        <v>1997600</v>
+        <v>2047300</v>
       </c>
       <c r="F76" s="3">
-        <v>2129500</v>
+        <v>2182500</v>
       </c>
       <c r="G76" s="3">
-        <v>2156900</v>
+        <v>2210500</v>
       </c>
       <c r="H76" s="3">
-        <v>2217600</v>
+        <v>2272800</v>
       </c>
       <c r="I76" s="3">
-        <v>2521500</v>
+        <v>2584300</v>
       </c>
       <c r="J76" s="3">
-        <v>2533600</v>
+        <v>2596700</v>
       </c>
       <c r="K76" s="3">
         <v>2556300</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>574600</v>
+        <v>588900</v>
       </c>
       <c r="E81" s="3">
-        <v>420000</v>
+        <v>430400</v>
       </c>
       <c r="F81" s="3">
-        <v>602600</v>
+        <v>617600</v>
       </c>
       <c r="G81" s="3">
-        <v>388900</v>
+        <v>398600</v>
       </c>
       <c r="H81" s="3">
-        <v>221700</v>
+        <v>227200</v>
       </c>
       <c r="I81" s="3">
-        <v>189100</v>
+        <v>193800</v>
       </c>
       <c r="J81" s="3">
-        <v>72600</v>
+        <v>74400</v>
       </c>
       <c r="K81" s="3">
         <v>151900</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>720300</v>
+        <v>738200</v>
       </c>
       <c r="E83" s="3">
-        <v>859300</v>
+        <v>880700</v>
       </c>
       <c r="F83" s="3">
-        <v>721500</v>
+        <v>739400</v>
       </c>
       <c r="G83" s="3">
-        <v>900400</v>
+        <v>922900</v>
       </c>
       <c r="H83" s="3">
-        <v>1305100</v>
+        <v>1337500</v>
       </c>
       <c r="I83" s="3">
-        <v>816700</v>
+        <v>837000</v>
       </c>
       <c r="J83" s="3">
-        <v>907700</v>
+        <v>930300</v>
       </c>
       <c r="K83" s="3">
         <v>956300</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1291500</v>
+        <v>1323700</v>
       </c>
       <c r="E89" s="3">
-        <v>1423500</v>
+        <v>1458900</v>
       </c>
       <c r="F89" s="3">
-        <v>1402200</v>
+        <v>1437100</v>
       </c>
       <c r="G89" s="3">
-        <v>1269400</v>
+        <v>1301000</v>
       </c>
       <c r="H89" s="3">
-        <v>1253900</v>
+        <v>1285100</v>
       </c>
       <c r="I89" s="3">
-        <v>1067700</v>
+        <v>1094300</v>
       </c>
       <c r="J89" s="3">
-        <v>865200</v>
+        <v>886700</v>
       </c>
       <c r="K89" s="3">
         <v>1112200</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-671500</v>
+        <v>-688300</v>
       </c>
       <c r="E91" s="3">
-        <v>-691100</v>
+        <v>-708300</v>
       </c>
       <c r="F91" s="3">
-        <v>-633300</v>
+        <v>-649100</v>
       </c>
       <c r="G91" s="3">
-        <v>-721700</v>
+        <v>-739700</v>
       </c>
       <c r="H91" s="3">
-        <v>-715200</v>
+        <v>-733000</v>
       </c>
       <c r="I91" s="3">
-        <v>-778000</v>
+        <v>-797400</v>
       </c>
       <c r="J91" s="3">
-        <v>-977200</v>
+        <v>-1001500</v>
       </c>
       <c r="K91" s="3">
         <v>-708500</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-653600</v>
+        <v>-669900</v>
       </c>
       <c r="E94" s="3">
-        <v>-690000</v>
+        <v>-707200</v>
       </c>
       <c r="F94" s="3">
-        <v>-470600</v>
+        <v>-482400</v>
       </c>
       <c r="G94" s="3">
-        <v>-789000</v>
+        <v>-808700</v>
       </c>
       <c r="H94" s="3">
-        <v>-681500</v>
+        <v>-698500</v>
       </c>
       <c r="I94" s="3">
-        <v>-779500</v>
+        <v>-798900</v>
       </c>
       <c r="J94" s="3">
-        <v>-986400</v>
+        <v>-1010900</v>
       </c>
       <c r="K94" s="3">
         <v>-702000</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-270100</v>
+        <v>-276800</v>
       </c>
       <c r="E96" s="3">
-        <v>-270100</v>
+        <v>-276800</v>
       </c>
       <c r="F96" s="3">
-        <v>-460500</v>
+        <v>-471900</v>
       </c>
       <c r="G96" s="3">
-        <v>-278700</v>
+        <v>-285700</v>
       </c>
       <c r="H96" s="3">
-        <v>-269100</v>
+        <v>-275800</v>
       </c>
       <c r="I96" s="3">
-        <v>-184900</v>
+        <v>-189500</v>
       </c>
       <c r="J96" s="3">
-        <v>-84400</v>
+        <v>-86500</v>
       </c>
       <c r="K96" s="3">
         <v>-53100</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-774100</v>
+        <v>-793400</v>
       </c>
       <c r="E100" s="3">
-        <v>-779600</v>
+        <v>-799000</v>
       </c>
       <c r="F100" s="3">
-        <v>-806700</v>
+        <v>-826800</v>
       </c>
       <c r="G100" s="3">
-        <v>-1063200</v>
+        <v>-1089700</v>
       </c>
       <c r="H100" s="3">
-        <v>-598800</v>
+        <v>-613700</v>
       </c>
       <c r="I100" s="3">
-        <v>-518700</v>
+        <v>-531600</v>
       </c>
       <c r="J100" s="3">
-        <v>-184900</v>
+        <v>-189500</v>
       </c>
       <c r="K100" s="3">
         <v>-124100</v>
@@ -4461,7 +4461,7 @@
         <v>-1100</v>
       </c>
       <c r="G101" s="3">
-        <v>-3000</v>
+        <v>-3100</v>
       </c>
       <c r="H101" s="3">
         <v>-2200</v>
@@ -4470,7 +4470,7 @@
         <v>300</v>
       </c>
       <c r="J101" s="3">
-        <v>-5100</v>
+        <v>-5200</v>
       </c>
       <c r="K101" s="3">
         <v>-700</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-136400</v>
+        <v>-139800</v>
       </c>
       <c r="E102" s="3">
-        <v>-43900</v>
+        <v>-45000</v>
       </c>
       <c r="F102" s="3">
-        <v>123700</v>
+        <v>126800</v>
       </c>
       <c r="G102" s="3">
-        <v>-585800</v>
+        <v>-600400</v>
       </c>
       <c r="H102" s="3">
-        <v>-28500</v>
+        <v>-29200</v>
       </c>
       <c r="I102" s="3">
-        <v>-230200</v>
+        <v>-235900</v>
       </c>
       <c r="J102" s="3">
-        <v>-311100</v>
+        <v>-318900</v>
       </c>
       <c r="K102" s="3">
         <v>285500</v>

--- a/AAII_Financials/Yearly/HLTOY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HLTOY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
   <si>
     <t>HLTOY</t>
   </si>
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>3842200</v>
+        <v>3834300</v>
       </c>
       <c r="E8" s="3">
-        <v>3827100</v>
+        <v>3692700</v>
       </c>
       <c r="F8" s="3">
-        <v>3695300</v>
+        <v>3794300</v>
       </c>
       <c r="G8" s="3">
-        <v>3609600</v>
+        <v>3986400</v>
       </c>
       <c r="H8" s="3">
-        <v>3658400</v>
+        <v>3706700</v>
       </c>
       <c r="I8" s="3">
-        <v>4207400</v>
+        <v>4349300</v>
       </c>
       <c r="J8" s="3">
-        <v>4205400</v>
+        <v>4559200</v>
       </c>
       <c r="K8" s="3">
         <v>4240300</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>359100</v>
+        <v>1467200</v>
       </c>
       <c r="E9" s="3">
-        <v>242700</v>
+        <v>1429700</v>
       </c>
       <c r="F9" s="3">
-        <v>191000</v>
+        <v>1431700</v>
       </c>
       <c r="G9" s="3">
-        <v>182200</v>
+        <v>1585700</v>
       </c>
       <c r="H9" s="3">
-        <v>155000</v>
+        <v>1482100</v>
       </c>
       <c r="I9" s="3">
-        <v>166800</v>
+        <v>1809600</v>
       </c>
       <c r="J9" s="3">
-        <v>181100</v>
+        <v>1880900</v>
       </c>
       <c r="K9" s="3">
         <v>194100</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>3483100</v>
+        <v>2367100</v>
       </c>
       <c r="E10" s="3">
-        <v>3584400</v>
+        <v>2263000</v>
       </c>
       <c r="F10" s="3">
-        <v>3504300</v>
+        <v>2362600</v>
       </c>
       <c r="G10" s="3">
-        <v>3427400</v>
+        <v>2400700</v>
       </c>
       <c r="H10" s="3">
-        <v>3503400</v>
+        <v>2224600</v>
       </c>
       <c r="I10" s="3">
-        <v>4040600</v>
+        <v>2539700</v>
       </c>
       <c r="J10" s="3">
-        <v>4024400</v>
+        <v>2678300</v>
       </c>
       <c r="K10" s="3">
         <v>4046200</v>
@@ -970,25 +970,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-1000</v>
+        <v>37900</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>38500</v>
       </c>
       <c r="F14" s="3">
-        <v>55800</v>
+        <v>-81700</v>
       </c>
       <c r="G14" s="3">
-        <v>-10900</v>
+        <v>342800</v>
       </c>
       <c r="H14" s="3">
-        <v>46300</v>
+        <v>143100</v>
       </c>
       <c r="I14" s="3">
-        <v>-2400</v>
+        <v>-300</v>
       </c>
       <c r="J14" s="3">
-        <v>44100</v>
+        <v>84500</v>
       </c>
       <c r="K14" s="3">
         <v>-19900</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>738200</v>
+        <v>736700</v>
       </c>
       <c r="E15" s="3">
-        <v>880700</v>
+        <v>849700</v>
       </c>
       <c r="F15" s="3">
-        <v>739400</v>
+        <v>759200</v>
       </c>
       <c r="G15" s="3">
-        <v>899500</v>
+        <v>823500</v>
       </c>
       <c r="H15" s="3">
-        <v>1263300</v>
+        <v>787200</v>
       </c>
       <c r="I15" s="3">
-        <v>903200</v>
+        <v>865200</v>
       </c>
       <c r="J15" s="3">
-        <v>972700</v>
+        <v>940200</v>
       </c>
       <c r="K15" s="3">
         <v>956300</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3048400</v>
+        <v>3009800</v>
       </c>
       <c r="E17" s="3">
-        <v>3173100</v>
+        <v>3025200</v>
       </c>
       <c r="F17" s="3">
-        <v>2851400</v>
+        <v>3010900</v>
       </c>
       <c r="G17" s="3">
-        <v>3231600</v>
+        <v>3229500</v>
       </c>
       <c r="H17" s="3">
-        <v>3122000</v>
+        <v>3025200</v>
       </c>
       <c r="I17" s="3">
-        <v>3656500</v>
+        <v>3800800</v>
       </c>
       <c r="J17" s="3">
-        <v>3745000</v>
+        <v>3992900</v>
       </c>
       <c r="K17" s="3">
         <v>3802100</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>793700</v>
+        <v>824500</v>
       </c>
       <c r="E18" s="3">
-        <v>654000</v>
+        <v>667500</v>
       </c>
       <c r="F18" s="3">
-        <v>843900</v>
+        <v>783400</v>
       </c>
       <c r="G18" s="3">
-        <v>377900</v>
+        <v>756900</v>
       </c>
       <c r="H18" s="3">
-        <v>536400</v>
+        <v>681400</v>
       </c>
       <c r="I18" s="3">
-        <v>550900</v>
+        <v>548500</v>
       </c>
       <c r="J18" s="3">
-        <v>460400</v>
+        <v>566300</v>
       </c>
       <c r="K18" s="3">
         <v>438200</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>4100</v>
+        <v>-3400</v>
       </c>
       <c r="E20" s="3">
-        <v>4800</v>
+        <v>-1700</v>
       </c>
       <c r="F20" s="3">
-        <v>2800</v>
+        <v>-1700</v>
       </c>
       <c r="G20" s="3">
-        <v>-2100</v>
+        <v>4400</v>
       </c>
       <c r="H20" s="3">
-        <v>19800</v>
+        <v>-16900</v>
       </c>
       <c r="I20" s="3">
-        <v>2300</v>
+        <v>-15500</v>
       </c>
       <c r="J20" s="3">
-        <v>-4300</v>
+        <v>-5300</v>
       </c>
       <c r="K20" s="3">
         <v>-2300</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1535900</v>
+        <v>1564600</v>
       </c>
       <c r="E21" s="3">
-        <v>1539300</v>
+        <v>1519000</v>
       </c>
       <c r="F21" s="3">
-        <v>1585900</v>
+        <v>1544300</v>
       </c>
       <c r="G21" s="3">
-        <v>1298500</v>
+        <v>1576000</v>
       </c>
       <c r="H21" s="3">
-        <v>1893500</v>
+        <v>1485600</v>
       </c>
       <c r="I21" s="3">
-        <v>1390100</v>
+        <v>1429200</v>
       </c>
       <c r="J21" s="3">
-        <v>1386200</v>
+        <v>1511800</v>
       </c>
       <c r="K21" s="3">
         <v>1391900</v>
@@ -1275,25 +1275,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>23000</v>
+        <v>16800</v>
       </c>
       <c r="E22" s="3">
-        <v>44200</v>
+        <v>37700</v>
       </c>
       <c r="F22" s="3">
-        <v>49800</v>
+        <v>49700</v>
       </c>
       <c r="G22" s="3">
-        <v>62200</v>
+        <v>65600</v>
       </c>
       <c r="H22" s="3">
-        <v>102800</v>
+        <v>99000</v>
       </c>
       <c r="I22" s="3">
-        <v>95400</v>
+        <v>93800</v>
       </c>
       <c r="J22" s="3">
-        <v>154100</v>
+        <v>161500</v>
       </c>
       <c r="K22" s="3">
         <v>162100</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>774800</v>
+        <v>773200</v>
       </c>
       <c r="E23" s="3">
-        <v>614600</v>
+        <v>593000</v>
       </c>
       <c r="F23" s="3">
-        <v>796800</v>
+        <v>818200</v>
       </c>
       <c r="G23" s="3">
-        <v>313600</v>
+        <v>346300</v>
       </c>
       <c r="H23" s="3">
-        <v>453500</v>
+        <v>459400</v>
       </c>
       <c r="I23" s="3">
-        <v>457900</v>
+        <v>473300</v>
       </c>
       <c r="J23" s="3">
-        <v>302000</v>
+        <v>327400</v>
       </c>
       <c r="K23" s="3">
         <v>273900</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>185900</v>
+        <v>185500</v>
       </c>
       <c r="E24" s="3">
-        <v>184100</v>
+        <v>177600</v>
       </c>
       <c r="F24" s="3">
-        <v>258700</v>
+        <v>265700</v>
       </c>
       <c r="G24" s="3">
-        <v>50800</v>
+        <v>56100</v>
       </c>
       <c r="H24" s="3">
-        <v>102200</v>
+        <v>103600</v>
       </c>
       <c r="I24" s="3">
-        <v>183600</v>
+        <v>189800</v>
       </c>
       <c r="J24" s="3">
-        <v>163500</v>
+        <v>177200</v>
       </c>
       <c r="K24" s="3">
         <v>182700</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>588900</v>
+        <v>587700</v>
       </c>
       <c r="E26" s="3">
-        <v>430500</v>
+        <v>415400</v>
       </c>
       <c r="F26" s="3">
-        <v>538100</v>
+        <v>552500</v>
       </c>
       <c r="G26" s="3">
-        <v>262700</v>
+        <v>290200</v>
       </c>
       <c r="H26" s="3">
-        <v>351200</v>
+        <v>355900</v>
       </c>
       <c r="I26" s="3">
-        <v>274200</v>
+        <v>283500</v>
       </c>
       <c r="J26" s="3">
-        <v>138600</v>
+        <v>150200</v>
       </c>
       <c r="K26" s="3">
         <v>91100</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>588900</v>
+        <v>587700</v>
       </c>
       <c r="E27" s="3">
-        <v>430400</v>
+        <v>415300</v>
       </c>
       <c r="F27" s="3">
-        <v>502500</v>
+        <v>634100</v>
       </c>
       <c r="G27" s="3">
-        <v>245200</v>
+        <v>440200</v>
       </c>
       <c r="H27" s="3">
-        <v>530900</v>
+        <v>230200</v>
       </c>
       <c r="I27" s="3">
-        <v>284300</v>
+        <v>200400</v>
       </c>
       <c r="J27" s="3">
-        <v>187700</v>
+        <v>80700</v>
       </c>
       <c r="K27" s="3">
         <v>151900</v>
@@ -1589,26 +1589,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>115100</v>
+        <v>118200</v>
       </c>
       <c r="G29" s="3">
-        <v>153400</v>
+        <v>169400</v>
       </c>
       <c r="H29" s="3">
-        <v>-303700</v>
+        <v>-307700</v>
       </c>
       <c r="I29" s="3">
-        <v>-90500</v>
+        <v>-93500</v>
       </c>
       <c r="J29" s="3">
-        <v>-113300</v>
+        <v>-122800</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-4100</v>
+        <v>3400</v>
       </c>
       <c r="E32" s="3">
-        <v>-4800</v>
+        <v>1700</v>
       </c>
       <c r="F32" s="3">
-        <v>-2800</v>
+        <v>1700</v>
       </c>
       <c r="G32" s="3">
-        <v>2100</v>
+        <v>-4400</v>
       </c>
       <c r="H32" s="3">
-        <v>-19800</v>
+        <v>16900</v>
       </c>
       <c r="I32" s="3">
-        <v>-2300</v>
+        <v>15500</v>
       </c>
       <c r="J32" s="3">
-        <v>4300</v>
+        <v>5300</v>
       </c>
       <c r="K32" s="3">
         <v>2300</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>588900</v>
+        <v>587700</v>
       </c>
       <c r="E33" s="3">
-        <v>430400</v>
+        <v>415300</v>
       </c>
       <c r="F33" s="3">
-        <v>617600</v>
+        <v>634100</v>
       </c>
       <c r="G33" s="3">
-        <v>398600</v>
+        <v>440200</v>
       </c>
       <c r="H33" s="3">
-        <v>227200</v>
+        <v>230200</v>
       </c>
       <c r="I33" s="3">
-        <v>193800</v>
+        <v>200400</v>
       </c>
       <c r="J33" s="3">
-        <v>74400</v>
+        <v>80700</v>
       </c>
       <c r="K33" s="3">
         <v>151900</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>588900</v>
+        <v>587700</v>
       </c>
       <c r="E35" s="3">
-        <v>430400</v>
+        <v>415300</v>
       </c>
       <c r="F35" s="3">
-        <v>617600</v>
+        <v>634100</v>
       </c>
       <c r="G35" s="3">
-        <v>398600</v>
+        <v>440200</v>
       </c>
       <c r="H35" s="3">
-        <v>227200</v>
+        <v>230200</v>
       </c>
       <c r="I35" s="3">
-        <v>193800</v>
+        <v>200400</v>
       </c>
       <c r="J35" s="3">
-        <v>74400</v>
+        <v>80700</v>
       </c>
       <c r="K35" s="3">
         <v>151900</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>513800</v>
+        <v>512800</v>
       </c>
       <c r="E41" s="3">
-        <v>653600</v>
+        <v>630700</v>
       </c>
       <c r="F41" s="3">
-        <v>698600</v>
+        <v>717300</v>
       </c>
       <c r="G41" s="3">
-        <v>571700</v>
+        <v>631400</v>
       </c>
       <c r="H41" s="3">
-        <v>1172200</v>
+        <v>1187600</v>
       </c>
       <c r="I41" s="3">
-        <v>1201400</v>
+        <v>1241900</v>
       </c>
       <c r="J41" s="3">
-        <v>1437300</v>
+        <v>1558200</v>
       </c>
       <c r="K41" s="3">
         <v>1720400</v>
@@ -2041,22 +2041,22 @@
         <v>6200</v>
       </c>
       <c r="E42" s="3">
-        <v>5300</v>
+        <v>5100</v>
       </c>
       <c r="F42" s="3">
-        <v>6200</v>
+        <v>6400</v>
       </c>
       <c r="G42" s="3">
-        <v>6000</v>
+        <v>6600</v>
       </c>
       <c r="H42" s="3">
-        <v>6300</v>
+        <v>6400</v>
       </c>
       <c r="I42" s="3">
-        <v>5600</v>
+        <v>5800</v>
       </c>
       <c r="J42" s="3">
-        <v>6500</v>
+        <v>7100</v>
       </c>
       <c r="K42" s="3">
         <v>6100</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>696500</v>
+        <v>702200</v>
       </c>
       <c r="E43" s="3">
-        <v>604900</v>
+        <v>590500</v>
       </c>
       <c r="F43" s="3">
-        <v>667800</v>
+        <v>722300</v>
       </c>
       <c r="G43" s="3">
-        <v>567900</v>
+        <v>665200</v>
       </c>
       <c r="H43" s="3">
-        <v>795700</v>
+        <v>842700</v>
       </c>
       <c r="I43" s="3">
-        <v>802800</v>
+        <v>863200</v>
       </c>
       <c r="J43" s="3">
-        <v>797100</v>
+        <v>986800</v>
       </c>
       <c r="K43" s="3">
         <v>792600</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>65200</v>
+        <v>65100</v>
       </c>
       <c r="E44" s="3">
-        <v>59800</v>
+        <v>57700</v>
       </c>
       <c r="F44" s="3">
-        <v>42100</v>
+        <v>43200</v>
       </c>
       <c r="G44" s="3">
-        <v>29800</v>
+        <v>32900</v>
       </c>
       <c r="H44" s="3">
-        <v>56800</v>
+        <v>57600</v>
       </c>
       <c r="I44" s="3">
-        <v>90800</v>
+        <v>93900</v>
       </c>
       <c r="J44" s="3">
-        <v>101100</v>
+        <v>109600</v>
       </c>
       <c r="K44" s="3">
         <v>104100</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>85300</v>
+        <v>22700</v>
       </c>
       <c r="E45" s="3">
-        <v>67100</v>
+        <v>21300</v>
       </c>
       <c r="F45" s="3">
-        <v>127200</v>
+        <v>34800</v>
       </c>
       <c r="G45" s="3">
-        <v>105400</v>
+        <v>782300</v>
       </c>
       <c r="H45" s="3">
-        <v>158800</v>
+        <v>56100</v>
       </c>
       <c r="I45" s="3">
-        <v>183900</v>
+        <v>148700</v>
       </c>
       <c r="J45" s="3">
-        <v>292000</v>
+        <v>118000</v>
       </c>
       <c r="K45" s="3">
         <v>337700</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1367000</v>
+        <v>1364200</v>
       </c>
       <c r="E46" s="3">
-        <v>1390700</v>
+        <v>1341900</v>
       </c>
       <c r="F46" s="3">
-        <v>1541800</v>
+        <v>1583100</v>
       </c>
       <c r="G46" s="3">
-        <v>1280800</v>
+        <v>2156500</v>
       </c>
       <c r="H46" s="3">
-        <v>2189800</v>
+        <v>2218700</v>
       </c>
       <c r="I46" s="3">
-        <v>2284500</v>
+        <v>2440000</v>
       </c>
       <c r="J46" s="3">
-        <v>2634100</v>
+        <v>2855700</v>
       </c>
       <c r="K46" s="3">
         <v>2960700</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>99100</v>
+        <v>1400</v>
       </c>
       <c r="E47" s="3">
-        <v>105200</v>
+        <v>600</v>
       </c>
       <c r="F47" s="3">
-        <v>103100</v>
+        <v>100</v>
       </c>
       <c r="G47" s="3">
-        <v>107700</v>
+        <v>100</v>
       </c>
       <c r="H47" s="3">
-        <v>138600</v>
+        <v>100</v>
       </c>
       <c r="I47" s="3">
-        <v>181500</v>
+        <v>100</v>
       </c>
       <c r="J47" s="3">
-        <v>91500</v>
+        <v>100</v>
       </c>
       <c r="K47" s="3">
         <v>93000</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2710000</v>
+        <v>2704400</v>
       </c>
       <c r="E48" s="3">
-        <v>2600300</v>
+        <v>2509000</v>
       </c>
       <c r="F48" s="3">
-        <v>2597300</v>
+        <v>2666900</v>
       </c>
       <c r="G48" s="3">
-        <v>2683400</v>
+        <v>2963500</v>
       </c>
       <c r="H48" s="3">
-        <v>3056900</v>
+        <v>3097200</v>
       </c>
       <c r="I48" s="3">
-        <v>3036000</v>
+        <v>3138400</v>
       </c>
       <c r="J48" s="3">
-        <v>3035800</v>
+        <v>3291200</v>
       </c>
       <c r="K48" s="3">
         <v>3095000</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1000900</v>
+        <v>998900</v>
       </c>
       <c r="E49" s="3">
-        <v>1116200</v>
+        <v>1077100</v>
       </c>
       <c r="F49" s="3">
-        <v>1233000</v>
+        <v>1266000</v>
       </c>
       <c r="G49" s="3">
-        <v>1268900</v>
+        <v>1401300</v>
       </c>
       <c r="H49" s="3">
-        <v>1249500</v>
+        <v>1266000</v>
       </c>
       <c r="I49" s="3">
-        <v>1470400</v>
+        <v>1520000</v>
       </c>
       <c r="J49" s="3">
-        <v>1633600</v>
+        <v>1771000</v>
       </c>
       <c r="K49" s="3">
         <v>1615200</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>290500</v>
+        <v>35800</v>
       </c>
       <c r="E52" s="3">
-        <v>280800</v>
+        <v>34400</v>
       </c>
       <c r="F52" s="3">
-        <v>303200</v>
+        <v>29700</v>
       </c>
       <c r="G52" s="3">
-        <v>1158500</v>
+        <v>32500</v>
       </c>
       <c r="H52" s="3">
-        <v>405200</v>
+        <v>31600</v>
       </c>
       <c r="I52" s="3">
-        <v>448200</v>
+        <v>73000</v>
       </c>
       <c r="J52" s="3">
-        <v>471400</v>
+        <v>73000</v>
       </c>
       <c r="K52" s="3">
         <v>451300</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>5467600</v>
+        <v>5456400</v>
       </c>
       <c r="E54" s="3">
-        <v>5493300</v>
+        <v>5300400</v>
       </c>
       <c r="F54" s="3">
-        <v>5778300</v>
+        <v>5933100</v>
       </c>
       <c r="G54" s="3">
-        <v>6499300</v>
+        <v>7177900</v>
       </c>
       <c r="H54" s="3">
-        <v>7039900</v>
+        <v>7132800</v>
       </c>
       <c r="I54" s="3">
-        <v>7420800</v>
+        <v>7671100</v>
       </c>
       <c r="J54" s="3">
-        <v>7866400</v>
+        <v>8528100</v>
       </c>
       <c r="K54" s="3">
         <v>8215200</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>959600</v>
+        <v>793300</v>
       </c>
       <c r="E57" s="3">
-        <v>968000</v>
+        <v>766100</v>
       </c>
       <c r="F57" s="3">
-        <v>906600</v>
+        <v>930900</v>
       </c>
       <c r="G57" s="3">
-        <v>797300</v>
+        <v>880500</v>
       </c>
       <c r="H57" s="3">
-        <v>1036700</v>
+        <v>1050400</v>
       </c>
       <c r="I57" s="3">
-        <v>1145300</v>
+        <v>1183900</v>
       </c>
       <c r="J57" s="3">
-        <v>1287500</v>
+        <v>1386000</v>
       </c>
       <c r="K57" s="3">
         <v>1480000</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>67300</v>
+        <v>67200</v>
       </c>
       <c r="E58" s="3">
-        <v>276000</v>
+        <v>266300</v>
       </c>
       <c r="F58" s="3">
-        <v>519500</v>
+        <v>533400</v>
       </c>
       <c r="G58" s="3">
-        <v>321400</v>
+        <v>355000</v>
       </c>
       <c r="H58" s="3">
-        <v>863200</v>
+        <v>874500</v>
       </c>
       <c r="I58" s="3">
-        <v>607000</v>
+        <v>627400</v>
       </c>
       <c r="J58" s="3">
-        <v>846800</v>
+        <v>918000</v>
       </c>
       <c r="K58" s="3">
         <v>199700</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>799200</v>
+        <v>635800</v>
       </c>
       <c r="E59" s="3">
-        <v>713500</v>
+        <v>510500</v>
       </c>
       <c r="F59" s="3">
-        <v>720300</v>
+        <v>576700</v>
       </c>
       <c r="G59" s="3">
-        <v>823600</v>
+        <v>890500</v>
       </c>
       <c r="H59" s="3">
-        <v>778800</v>
+        <v>407100</v>
       </c>
       <c r="I59" s="3">
-        <v>834900</v>
+        <v>461000</v>
       </c>
       <c r="J59" s="3">
-        <v>879500</v>
+        <v>449900</v>
       </c>
       <c r="K59" s="3">
         <v>967800</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1826200</v>
+        <v>1822500</v>
       </c>
       <c r="E60" s="3">
-        <v>1957600</v>
+        <v>1888900</v>
       </c>
       <c r="F60" s="3">
-        <v>2146300</v>
+        <v>2203800</v>
       </c>
       <c r="G60" s="3">
-        <v>1942300</v>
+        <v>2525700</v>
       </c>
       <c r="H60" s="3">
-        <v>2678600</v>
+        <v>2713900</v>
       </c>
       <c r="I60" s="3">
-        <v>2587100</v>
+        <v>2718700</v>
       </c>
       <c r="J60" s="3">
-        <v>3013800</v>
+        <v>3267300</v>
       </c>
       <c r="K60" s="3">
         <v>2647600</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1143700</v>
+        <v>1141400</v>
       </c>
       <c r="E61" s="3">
-        <v>1178000</v>
+        <v>1136700</v>
       </c>
       <c r="F61" s="3">
-        <v>1044400</v>
+        <v>1072300</v>
       </c>
       <c r="G61" s="3">
-        <v>1401600</v>
+        <v>1547900</v>
       </c>
       <c r="H61" s="3">
-        <v>1474100</v>
+        <v>1493500</v>
       </c>
       <c r="I61" s="3">
-        <v>1418400</v>
+        <v>1466200</v>
       </c>
       <c r="J61" s="3">
-        <v>1413500</v>
+        <v>1532400</v>
       </c>
       <c r="K61" s="3">
         <v>2106000</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>344700</v>
+        <v>130300</v>
       </c>
       <c r="E62" s="3">
-        <v>309800</v>
+        <v>150200</v>
       </c>
       <c r="F62" s="3">
-        <v>403300</v>
+        <v>211400</v>
       </c>
       <c r="G62" s="3">
-        <v>440700</v>
+        <v>262400</v>
       </c>
       <c r="H62" s="3">
-        <v>469200</v>
+        <v>193000</v>
       </c>
       <c r="I62" s="3">
-        <v>520700</v>
+        <v>233000</v>
       </c>
       <c r="J62" s="3">
-        <v>571100</v>
+        <v>271300</v>
       </c>
       <c r="K62" s="3">
         <v>584500</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>3315200</v>
+        <v>3307800</v>
       </c>
       <c r="E66" s="3">
-        <v>3446000</v>
+        <v>3324500</v>
       </c>
       <c r="F66" s="3">
-        <v>3595800</v>
+        <v>3690200</v>
       </c>
       <c r="G66" s="3">
-        <v>4288700</v>
+        <v>4560400</v>
       </c>
       <c r="H66" s="3">
-        <v>4767100</v>
+        <v>4682900</v>
       </c>
       <c r="I66" s="3">
-        <v>4836600</v>
+        <v>4723200</v>
       </c>
       <c r="J66" s="3">
-        <v>5269700</v>
+        <v>5418800</v>
       </c>
       <c r="K66" s="3">
         <v>5658900</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>550800</v>
+        <v>564900</v>
       </c>
       <c r="E72" s="3">
-        <v>431400</v>
+        <v>421600</v>
       </c>
       <c r="F72" s="3">
-        <v>4230600</v>
+        <v>4384300</v>
       </c>
       <c r="G72" s="3">
-        <v>4216500</v>
+        <v>4693200</v>
       </c>
       <c r="H72" s="3">
-        <v>4179600</v>
+        <v>4285800</v>
       </c>
       <c r="I72" s="3">
-        <v>4410900</v>
+        <v>4573800</v>
       </c>
       <c r="J72" s="3">
-        <v>4197300</v>
+        <v>4739000</v>
       </c>
       <c r="K72" s="3">
         <v>4124200</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2152400</v>
+        <v>2148000</v>
       </c>
       <c r="E76" s="3">
-        <v>2047300</v>
+        <v>1975400</v>
       </c>
       <c r="F76" s="3">
-        <v>2182500</v>
+        <v>2241000</v>
       </c>
       <c r="G76" s="3">
-        <v>2210500</v>
+        <v>2441300</v>
       </c>
       <c r="H76" s="3">
-        <v>2272800</v>
+        <v>2302800</v>
       </c>
       <c r="I76" s="3">
-        <v>2584300</v>
+        <v>2671400</v>
       </c>
       <c r="J76" s="3">
-        <v>2596700</v>
+        <v>2815100</v>
       </c>
       <c r="K76" s="3">
         <v>2556300</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>588900</v>
+        <v>587700</v>
       </c>
       <c r="E81" s="3">
-        <v>430400</v>
+        <v>415300</v>
       </c>
       <c r="F81" s="3">
-        <v>617600</v>
+        <v>634100</v>
       </c>
       <c r="G81" s="3">
-        <v>398600</v>
+        <v>440200</v>
       </c>
       <c r="H81" s="3">
-        <v>227200</v>
+        <v>230200</v>
       </c>
       <c r="I81" s="3">
-        <v>193800</v>
+        <v>200400</v>
       </c>
       <c r="J81" s="3">
-        <v>74400</v>
+        <v>80700</v>
       </c>
       <c r="K81" s="3">
         <v>151900</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>738200</v>
+        <v>465100</v>
       </c>
       <c r="E83" s="3">
-        <v>880700</v>
+        <v>552800</v>
       </c>
       <c r="F83" s="3">
-        <v>739400</v>
+        <v>492000</v>
       </c>
       <c r="G83" s="3">
-        <v>922900</v>
+        <v>590600</v>
       </c>
       <c r="H83" s="3">
-        <v>1337500</v>
+        <v>787200</v>
       </c>
       <c r="I83" s="3">
-        <v>837000</v>
+        <v>865200</v>
       </c>
       <c r="J83" s="3">
-        <v>930300</v>
+        <v>690900</v>
       </c>
       <c r="K83" s="3">
         <v>956300</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1323700</v>
+        <v>1321000</v>
       </c>
       <c r="E89" s="3">
-        <v>1458900</v>
+        <v>1407700</v>
       </c>
       <c r="F89" s="3">
-        <v>1437100</v>
+        <v>1392200</v>
       </c>
       <c r="G89" s="3">
-        <v>1301000</v>
+        <v>1526500</v>
       </c>
       <c r="H89" s="3">
-        <v>1285100</v>
+        <v>1293700</v>
       </c>
       <c r="I89" s="3">
-        <v>1094300</v>
+        <v>1139800</v>
       </c>
       <c r="J89" s="3">
-        <v>886700</v>
+        <v>961300</v>
       </c>
       <c r="K89" s="3">
         <v>1112200</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-688300</v>
+        <v>-686900</v>
       </c>
       <c r="E91" s="3">
-        <v>-708300</v>
+        <v>-683400</v>
       </c>
       <c r="F91" s="3">
-        <v>-649100</v>
+        <v>-666400</v>
       </c>
       <c r="G91" s="3">
-        <v>-739700</v>
+        <v>-816900</v>
       </c>
       <c r="H91" s="3">
-        <v>-733000</v>
+        <v>-613500</v>
       </c>
       <c r="I91" s="3">
-        <v>-797400</v>
+        <v>-824300</v>
       </c>
       <c r="J91" s="3">
-        <v>-1001500</v>
+        <v>-1085700</v>
       </c>
       <c r="K91" s="3">
         <v>-708500</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-669900</v>
+        <v>-668500</v>
       </c>
       <c r="E94" s="3">
-        <v>-707200</v>
+        <v>-682400</v>
       </c>
       <c r="F94" s="3">
-        <v>-482400</v>
+        <v>-495300</v>
       </c>
       <c r="G94" s="3">
-        <v>-808700</v>
+        <v>-893100</v>
       </c>
       <c r="H94" s="3">
-        <v>-698500</v>
+        <v>-707700</v>
       </c>
       <c r="I94" s="3">
-        <v>-798900</v>
+        <v>-825900</v>
       </c>
       <c r="J94" s="3">
-        <v>-1010900</v>
+        <v>-1095900</v>
       </c>
       <c r="K94" s="3">
         <v>-702000</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-276800</v>
+        <v>276200</v>
       </c>
       <c r="E96" s="3">
-        <v>-276800</v>
+        <v>267100</v>
       </c>
       <c r="F96" s="3">
-        <v>-471900</v>
+        <v>355700</v>
       </c>
       <c r="G96" s="3">
-        <v>-285700</v>
+        <v>315500</v>
       </c>
       <c r="H96" s="3">
-        <v>-275800</v>
+        <v>247100</v>
       </c>
       <c r="I96" s="3">
-        <v>-189500</v>
+        <v>195900</v>
       </c>
       <c r="J96" s="3">
-        <v>-86500</v>
+        <v>93800</v>
       </c>
       <c r="K96" s="3">
         <v>-53100</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-793400</v>
+        <v>-791800</v>
       </c>
       <c r="E100" s="3">
-        <v>-799000</v>
+        <v>-771000</v>
       </c>
       <c r="F100" s="3">
-        <v>-826800</v>
+        <v>-849000</v>
       </c>
       <c r="G100" s="3">
-        <v>-1089700</v>
+        <v>-1203400</v>
       </c>
       <c r="H100" s="3">
-        <v>-613700</v>
+        <v>-621800</v>
       </c>
       <c r="I100" s="3">
-        <v>-531600</v>
+        <v>-549600</v>
       </c>
       <c r="J100" s="3">
-        <v>-189500</v>
+        <v>-205500</v>
       </c>
       <c r="K100" s="3">
         <v>-124100</v>
@@ -4455,13 +4455,13 @@
         <v>-200</v>
       </c>
       <c r="E101" s="3">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="F101" s="3">
         <v>-1100</v>
       </c>
       <c r="G101" s="3">
-        <v>-3100</v>
+        <v>-3400</v>
       </c>
       <c r="H101" s="3">
         <v>-2200</v>
@@ -4470,7 +4470,7 @@
         <v>300</v>
       </c>
       <c r="J101" s="3">
-        <v>-5200</v>
+        <v>-5600</v>
       </c>
       <c r="K101" s="3">
         <v>-700</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-139800</v>
+        <v>-139500</v>
       </c>
       <c r="E102" s="3">
-        <v>-45000</v>
+        <v>-43400</v>
       </c>
       <c r="F102" s="3">
-        <v>126800</v>
+        <v>46900</v>
       </c>
       <c r="G102" s="3">
-        <v>-600400</v>
+        <v>-573500</v>
       </c>
       <c r="H102" s="3">
-        <v>-29200</v>
+        <v>-38000</v>
       </c>
       <c r="I102" s="3">
-        <v>-235900</v>
+        <v>-235300</v>
       </c>
       <c r="J102" s="3">
-        <v>-318900</v>
+        <v>-345700</v>
       </c>
       <c r="K102" s="3">
         <v>285500</v>

--- a/AAII_Financials/Yearly/HLTOY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HLTOY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
   <si>
     <t>HLTOY</t>
   </si>
@@ -656,207 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3717600</v>
+      </c>
+      <c r="E8" s="3">
         <v>3834300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3692700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3794300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3986400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3706700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4349300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4559200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4240300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3984100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4424300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4849500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4754700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5914000</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1467200</v>
+        <v>1372900</v>
       </c>
       <c r="E9" s="3">
+        <v>1477800</v>
+      </c>
+      <c r="F9" s="3">
         <v>1429700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1431700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1585700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1482100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1809600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1880900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>194100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>168300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>146400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>148100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1009900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1272100</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2367100</v>
+        <v>2344700</v>
       </c>
       <c r="E10" s="3">
+        <v>2356500</v>
+      </c>
+      <c r="F10" s="3">
         <v>2263000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2362600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2400700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2224600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2539700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2678300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4046200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3815800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4277800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4701400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3744700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4641900</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,8 +886,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -918,9 +931,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -963,99 +979,108 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E14" s="3">
         <v>37900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>38500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-81700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>342800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>143100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>84500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-19900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>20300</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-100</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>728100</v>
+      </c>
+      <c r="E15" s="3">
         <v>736700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>849700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>759200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>823500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>787200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>865200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>940200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>956300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>846700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>899200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1007800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>898600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1537900</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3009800</v>
+        <v>2995200</v>
       </c>
       <c r="E17" s="3">
+        <v>3008400</v>
+      </c>
+      <c r="F17" s="3">
         <v>3025200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3010900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3229500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3025200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3800800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3992900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3802100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3605200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3759100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4448200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4123900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5500100</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>824500</v>
+        <v>722300</v>
       </c>
       <c r="E18" s="3">
+        <v>825900</v>
+      </c>
+      <c r="F18" s="3">
         <v>667500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>783400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>756900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>681400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>548500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>566300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>438200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>378900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>665200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>401300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>630800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>413900</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1179,233 +1211,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-3400</v>
+        <v>17400</v>
       </c>
       <c r="E20" s="3">
-        <v>-1700</v>
+        <v>14800</v>
       </c>
       <c r="F20" s="3">
         <v>-1700</v>
       </c>
       <c r="G20" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="H20" s="3">
         <v>4400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-16900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-15500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-5300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>33400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>10200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>273100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>265800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>61700</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1564600</v>
+        <v>1433100</v>
       </c>
       <c r="E21" s="3">
+        <v>1547800</v>
+      </c>
+      <c r="F21" s="3">
         <v>1519000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1544300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1576000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1485600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1429200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1511800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1391900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1242600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1576600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1678100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1796600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2014600</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>16800</v>
-      </c>
-      <c r="E22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3">
         <v>37700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>49700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>65600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>99000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>93800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>161500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>162100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>160700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>228900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>297900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>271500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>340500</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>702600</v>
+      </c>
+      <c r="E23" s="3">
         <v>773200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>593000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>818200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>346300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>459400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>473300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>327400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>273900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>251600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>446400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>376600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>625100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>135100</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>206900</v>
+      </c>
+      <c r="E24" s="3">
         <v>185500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>177600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>265700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>56100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>103600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>189800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>177200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>182700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>120300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>139900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>25000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>114100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>151100</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>495700</v>
+      </c>
+      <c r="E26" s="3">
         <v>587700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>415400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>552500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>290200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>355900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>283500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>150200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>91100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>131400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>306600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>351600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>511000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-16000</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>495700</v>
+      </c>
+      <c r="E27" s="3">
         <v>587700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>415300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>634100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>440200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>230200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>200400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>80700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>151900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>155100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>301900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>344300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>483300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>140500</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1596,41 +1656,44 @@
         <v>0</v>
       </c>
       <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
         <v>118200</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>169400</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-307700</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-93500</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-122800</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="M29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>34600</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>34800</v>
       </c>
-      <c r="P29" s="3" t="s">
+      <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,99 +1784,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>3400</v>
+        <v>-17400</v>
       </c>
       <c r="E32" s="3">
-        <v>1700</v>
+        <v>-14800</v>
       </c>
       <c r="F32" s="3">
         <v>1700</v>
       </c>
       <c r="G32" s="3">
+        <v>1700</v>
+      </c>
+      <c r="H32" s="3">
         <v>-4400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>16900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>15500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>5300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-33400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-10200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-273100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-265800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-61700</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>495700</v>
+      </c>
+      <c r="E33" s="3">
         <v>587700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>415300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>634100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>440200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>230200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>200400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>80700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>151900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>155100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>301900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>378800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>518100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>140500</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>495700</v>
+      </c>
+      <c r="E35" s="3">
         <v>587700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>415300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>634100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>440200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>230200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>200400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>80700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>151900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>155100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>301900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>378800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>518100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>140500</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,289 +2072,308 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>483500</v>
+      </c>
+      <c r="E41" s="3">
         <v>512800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>630700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>717300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>631400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1187600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1241900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1558200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1720400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1350000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1704800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3455300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1278500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4600</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E42" s="3">
         <v>6200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>5100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>6400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>6600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>6400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>5800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>7100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>6100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>6900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>4200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>19700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1286700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1212500</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>664600</v>
+      </c>
+      <c r="E43" s="3">
         <v>702200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>590500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>722300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>665200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>842700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>863200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>986800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>792600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>743800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>773300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1682600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1007700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1203500</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>52900</v>
+      </c>
+      <c r="E44" s="3">
         <v>65100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>57700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>43200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>32900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>57600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>93900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>109600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>104100</v>
-      </c>
-      <c r="L44" s="3">
-        <v>99200</v>
       </c>
       <c r="M44" s="3">
         <v>99200</v>
       </c>
       <c r="N44" s="3">
+        <v>99200</v>
+      </c>
+      <c r="O44" s="3">
         <v>232100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>244600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>146700</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>22700</v>
+        <v>31600</v>
       </c>
       <c r="E45" s="3">
+        <v>27000</v>
+      </c>
+      <c r="F45" s="3">
         <v>21300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>34800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>782300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>56100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>148700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>118000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>337700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>260500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>234300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>552000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>497900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>136600</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1317500</v>
+      </c>
+      <c r="E46" s="3">
         <v>1364200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1341900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1583100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2156500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2218700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2440000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2855700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2960700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2460400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2815900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2983400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2614700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2704000</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E47" s="3">
         <v>1400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>600</v>
-      </c>
-      <c r="F47" s="3">
-        <v>100</v>
       </c>
       <c r="G47" s="3">
         <v>100</v>
@@ -2284,116 +2388,125 @@
         <v>100</v>
       </c>
       <c r="K47" s="3">
+        <v>100</v>
+      </c>
+      <c r="L47" s="3">
         <v>93000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>90100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>118100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>132800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>243500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>169600</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2577900</v>
+      </c>
+      <c r="E48" s="3">
         <v>2704400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2509000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2666900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2963500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3097200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3138400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3291200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3095000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3012000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3503900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7844400</v>
       </c>
-      <c r="O48" s="3" t="s">
+      <c r="P48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5080200</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>915200</v>
+      </c>
+      <c r="E49" s="3">
         <v>998900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1077100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1266000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1401300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1266000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1520000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1771000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1615200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1615700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1862500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2953200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3338100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1767200</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,54 +2597,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>34200</v>
+      </c>
+      <c r="E52" s="3">
         <v>35800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>34400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>29700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>32500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>31600</v>
-      </c>
-      <c r="I52" s="3">
-        <v>73000</v>
       </c>
       <c r="J52" s="3">
         <v>73000</v>
       </c>
       <c r="K52" s="3">
+        <v>73000</v>
+      </c>
+      <c r="L52" s="3">
         <v>451300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>437100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>511500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>564500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>676100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>950000</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5171500</v>
+      </c>
+      <c r="E54" s="3">
         <v>5456400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5300400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5933100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7177900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7132800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7671100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8528100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8215200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7615400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8811800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>9382200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>9185900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>10671000</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,278 +2784,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>761100</v>
+      </c>
+      <c r="E57" s="3">
         <v>793300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>766100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>930900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>880500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1050400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1183900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1386000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1480000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1227500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1101000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1104900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>861400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>879900</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>65600</v>
+      </c>
+      <c r="E58" s="3">
         <v>67200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>266300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>533400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>355000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>874500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>627400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>918000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>199700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>442500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>525500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>478400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1554300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>895500</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>547800</v>
+      </c>
+      <c r="E59" s="3">
         <v>635800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>510500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>576700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>890500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>407100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>461000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>449900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>967800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>870600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1122800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1296700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1550400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1110200</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1705600</v>
+      </c>
+      <c r="E60" s="3">
         <v>1822500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1888900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2203800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2525700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2713900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2718700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3267300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2647600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2540700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2749200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2880000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3367700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2885600</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1074500</v>
+      </c>
+      <c r="E61" s="3">
         <v>1141400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1136700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1072300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1547900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1493500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1466200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1532400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2106000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1792100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2453600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3058100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2893400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4858500</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>160700</v>
+      </c>
+      <c r="E62" s="3">
         <v>130300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>150200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>211400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>262400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>193000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>233000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>271300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>584500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>619100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>788000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>858000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>868400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>864200</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3137300</v>
+      </c>
+      <c r="E66" s="3">
         <v>3307800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3324500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3690200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4560400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4682900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4723200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5418800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5658900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5311400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6415900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7085100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7430400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9047000</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3258,9 +3425,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>663800</v>
+      </c>
+      <c r="E72" s="3">
         <v>564900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>421600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>4384300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4693200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4285800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4573800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>4739000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4124200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3779400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4027600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>4004500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>6941000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3466400</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2034300</v>
+      </c>
+      <c r="E76" s="3">
         <v>2148000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1975400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2241000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2441300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2302800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2671400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2815100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2556300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2303900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2396000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2297100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1755500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1624000</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>495700</v>
+      </c>
+      <c r="E81" s="3">
         <v>587700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>415300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>634100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>440200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>230200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>200400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>80700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>151900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>155100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>301900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>378800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>518100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>140500</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,53 +3885,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>487400</v>
+      </c>
+      <c r="E83" s="3">
         <v>465100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>552800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>492000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>590600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>787200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>865200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>690900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>956300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>846700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>899200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1007800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>898600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1537900</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1141100</v>
+      </c>
+      <c r="E89" s="3">
         <v>1321000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1407700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1392200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1526500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1293700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1139800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>961300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1112200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>962800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1128800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1306100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1281300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1418200</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,53 +4241,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-620900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-686900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-683400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-666400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-816900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-613500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-824300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1085700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-708500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-672100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-681900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-723300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1166300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-841000</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-604700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-668500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-682400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-495300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-893100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-707700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-825900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1095900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-702000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-658800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-650400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>191800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>165100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1210200</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,38 +4453,39 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>307400</v>
+      </c>
+      <c r="E96" s="3">
         <v>276200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>267100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>355700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>315500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>247100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>195900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>93800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-53100</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -4265,9 +4498,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,142 +4642,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-533500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-791800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-771000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-849000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1203400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-621800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-549600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-205500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-124100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-500300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-403700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1155800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-914600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-581200</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-3400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-2200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-5600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>5000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-6700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-139500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-43400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>46900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-573500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-38000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-235300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-345700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>285500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-191300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>74100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>338200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>525100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-376700</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/HLTOY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HLTOY_YR_FIN.xlsx
@@ -656,219 +656,231 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>3717600</v>
+        <v>4067500</v>
       </c>
       <c r="E8" s="3">
+        <v>3451700</v>
+      </c>
+      <c r="F8" s="3">
         <v>3834300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3692700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3794300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3986400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3706700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4349300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4559200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4240300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3984100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4424300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4849500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4754700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5914000</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1372900</v>
+        <v>1370700</v>
       </c>
       <c r="E9" s="3">
+        <v>1239200</v>
+      </c>
+      <c r="F9" s="3">
         <v>1477800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1429700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1431700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1585700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1482100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1809600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1880900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>194100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>168300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>146400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>148100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1009900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1272100</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2344700</v>
+        <v>2696800</v>
       </c>
       <c r="E10" s="3">
+        <v>2212500</v>
+      </c>
+      <c r="F10" s="3">
         <v>2356500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2263000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2362600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2400700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2224600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2539700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2678300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4046200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3815800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4277800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4701400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3744700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4641900</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -887,8 +899,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -934,9 +947,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -982,105 +998,114 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>2400</v>
+        <v>26800</v>
       </c>
       <c r="E14" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F14" s="3">
         <v>37900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>38500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-81700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>342800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>143100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>84500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-19900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>20300</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-100</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>728100</v>
+        <v>683300</v>
       </c>
       <c r="E15" s="3">
+        <v>603200</v>
+      </c>
+      <c r="F15" s="3">
         <v>736700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>849700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>759200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>823500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>787200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>865200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>940200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>956300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>846700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>899200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1007800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>898600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1537900</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1121,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2995200</v>
+        <v>3080900</v>
       </c>
       <c r="E17" s="3">
+        <v>2610000</v>
+      </c>
+      <c r="F17" s="3">
         <v>3008400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3025200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3010900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3229500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3025200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3800800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3992900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3802100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3605200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3759100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4448200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4123900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5500100</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>722300</v>
+        <v>986600</v>
       </c>
       <c r="E18" s="3">
+        <v>841700</v>
+      </c>
+      <c r="F18" s="3">
         <v>825900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>667500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>783400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>756900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>681400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>548500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>566300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>438200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>378900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>665200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>401300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>630800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>413900</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1212,248 +1244,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>17400</v>
+        <v>6500</v>
       </c>
       <c r="E20" s="3">
+        <v>8200</v>
+      </c>
+      <c r="F20" s="3">
         <v>14800</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-1700</v>
       </c>
       <c r="G20" s="3">
         <v>-1700</v>
       </c>
       <c r="H20" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="I20" s="3">
         <v>4400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-16900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-15500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-5300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>33400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>10200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>273100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>265800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>61700</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1433100</v>
+        <v>1663500</v>
       </c>
       <c r="E21" s="3">
+        <v>1436700</v>
+      </c>
+      <c r="F21" s="3">
         <v>1547800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1519000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1544300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1576000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1485600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1429200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1511800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1391900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1242600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1576600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1678100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1796600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2014600</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="3">
+        <v>19800</v>
+      </c>
+      <c r="E22" s="3">
+        <v>17600</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>37700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>49700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>65600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>99000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>93800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>161500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>162100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>160700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>228900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>297900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>271500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>340500</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>702600</v>
+        <v>942900</v>
       </c>
       <c r="E23" s="3">
+        <v>826800</v>
+      </c>
+      <c r="F23" s="3">
         <v>773200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>593000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>818200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>346300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>459400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>473300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>327400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>273900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>251600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>446400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>376600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>625100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>135100</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>206900</v>
+        <v>90500</v>
       </c>
       <c r="E24" s="3">
+        <v>188500</v>
+      </c>
+      <c r="F24" s="3">
         <v>185500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>177600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>265700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>56100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>103600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>189800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>177200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>182700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>120300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>139900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>25000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>114100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>151100</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1499,105 +1547,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>495700</v>
+        <v>852400</v>
       </c>
       <c r="E26" s="3">
+        <v>638300</v>
+      </c>
+      <c r="F26" s="3">
         <v>587700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>415400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>552500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>290200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>355900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>283500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>150200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>91100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>131400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>306600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>351600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>511000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-16000</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>588400</v>
+      </c>
+      <c r="E27" s="3">
         <v>495700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>587700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>415300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>634100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>440200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>230200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>200400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>80700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>151900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>155100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>301900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>344300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>483300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>140500</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1643,57 +1700,63 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>-264100</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>-142600</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
       </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>118200</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>169400</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-307700</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-93500</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-122800</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
+      <c r="N29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>34600</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>34800</v>
       </c>
-      <c r="Q29" s="3" t="s">
+      <c r="R29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1787,105 +1853,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-17400</v>
+        <v>-6500</v>
       </c>
       <c r="E32" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="F32" s="3">
         <v>-14800</v>
-      </c>
-      <c r="F32" s="3">
-        <v>1700</v>
       </c>
       <c r="G32" s="3">
         <v>1700</v>
       </c>
       <c r="H32" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I32" s="3">
         <v>-4400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>16900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>15500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>5300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-33400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-10200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-273100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-265800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-61700</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>588400</v>
+      </c>
+      <c r="E33" s="3">
         <v>495700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>587700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>415300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>634100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>440200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>230200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>200400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>80700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>151900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>155100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>301900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>378800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>518100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>140500</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1931,110 +2006,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>588400</v>
+      </c>
+      <c r="E35" s="3">
         <v>495700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>587700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>415300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>634100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>440200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>230200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>200400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>80700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>151900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>155100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>301900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>378800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>518100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>140500</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2073,310 +2158,329 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>611600</v>
+      </c>
+      <c r="E41" s="3">
         <v>483500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>512800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>630700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>717300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>631400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1187600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1241900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1558200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1720400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1350000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1704800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3455300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1278500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4600</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E42" s="3">
         <v>6100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>6200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>5100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>6400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>6600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>6400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>5800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>7100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>6100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>6900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>4200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>19700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1286700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1212500</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>821800</v>
+      </c>
+      <c r="E43" s="3">
         <v>664600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>702200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>590500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>722300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>665200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>842700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>863200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>986800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>792600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>743800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>773300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1682600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1007700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1203500</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>46800</v>
+      </c>
+      <c r="E44" s="3">
         <v>52900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>65100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>57700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>43200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>32900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>57600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>93900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>109600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>104100</v>
-      </c>
-      <c r="M44" s="3">
-        <v>99200</v>
       </c>
       <c r="N44" s="3">
         <v>99200</v>
       </c>
       <c r="O44" s="3">
+        <v>99200</v>
+      </c>
+      <c r="P44" s="3">
         <v>232100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>244600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>146700</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>31600</v>
+        <v>29000</v>
       </c>
       <c r="E45" s="3">
+        <v>22900</v>
+      </c>
+      <c r="F45" s="3">
         <v>27000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>21300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>34800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>782300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>56100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>148700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>118000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>337700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>260500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>234300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>552000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>497900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>136600</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1317500</v>
+        <v>1640100</v>
       </c>
       <c r="E46" s="3">
+        <v>1308800</v>
+      </c>
+      <c r="F46" s="3">
         <v>1364200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1341900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1583100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2156500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2218700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2440000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2855700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2960700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2460400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2815900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2983400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2614700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2704000</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E47" s="3">
         <v>2200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>600</v>
-      </c>
-      <c r="G47" s="3">
-        <v>100</v>
       </c>
       <c r="H47" s="3">
         <v>100</v>
@@ -2391,122 +2495,131 @@
         <v>100</v>
       </c>
       <c r="L47" s="3">
+        <v>100</v>
+      </c>
+      <c r="M47" s="3">
         <v>93000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>90100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>118100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>132800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>243500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>169600</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2966700</v>
+      </c>
+      <c r="E48" s="3">
         <v>2577900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2704400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2509000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2666900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2963500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3097200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3138400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3291200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3095000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3012000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3503900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7844400</v>
       </c>
-      <c r="P48" s="3" t="s">
+      <c r="Q48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5080200</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>989700</v>
+      </c>
+      <c r="E49" s="3">
         <v>915200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>998900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1077100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1266000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1401300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1266000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1520000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1771000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1615200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1615700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1862500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2953200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3338100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1767200</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2600,57 +2716,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>35500</v>
+      </c>
+      <c r="E52" s="3">
         <v>34200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>35800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>34400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>29700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>32500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>31600</v>
-      </c>
-      <c r="J52" s="3">
-        <v>73000</v>
       </c>
       <c r="K52" s="3">
         <v>73000</v>
       </c>
       <c r="L52" s="3">
+        <v>73000</v>
+      </c>
+      <c r="M52" s="3">
         <v>451300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>437100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>511500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>564500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>676100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>950000</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5919000</v>
+      </c>
+      <c r="E54" s="3">
         <v>5171500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5456400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5300400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5933100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7177900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7132800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7671100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8528100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8215200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7615400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8811800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>9382200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>9185900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>10671000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,296 +2914,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>791500</v>
+      </c>
+      <c r="E57" s="3">
         <v>761100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>793300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>766100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>930900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>880500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1050400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1183900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1386000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1480000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1227500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1101000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1104900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>861400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>879900</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>642900</v>
+      </c>
+      <c r="E58" s="3">
         <v>65600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>67200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>266300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>533400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>355000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>874500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>627400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>918000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>199700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>442500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>525500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>478400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1554300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>895500</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>672200</v>
+      </c>
+      <c r="E59" s="3">
         <v>547800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>635800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>510500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>576700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>890500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>407100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>461000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>449900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>967800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>870600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1122800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1296700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1550400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1110200</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2506000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1705600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1822500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1888900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2203800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2525700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2713900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2718700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3267300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2647600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2540700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2749200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2880000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3367700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2885600</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>604300</v>
+      </c>
+      <c r="E61" s="3">
         <v>1074500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1141400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1136700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1072300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1547900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1493500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1466200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1532400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2106000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1792100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2453600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3058100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2893400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4858500</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>122500</v>
+      </c>
+      <c r="E62" s="3">
         <v>160700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>130300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>150200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>211400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>262400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>193000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>233000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>271300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>584500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>619100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>788000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>858000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>868400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>864200</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3440500</v>
+      </c>
+      <c r="E66" s="3">
         <v>3137300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3307800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3324500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3690200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4560400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4682900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4723200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5418800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5658900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5311400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6415900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7085100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7430400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9047000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3380,9 +3544,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3428,9 +3595,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3476,57 +3646,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>829600</v>
+      </c>
+      <c r="E72" s="3">
         <v>663800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>564900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>421600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4384300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4693200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4285800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>4573800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4739000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4124200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3779400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>4027600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>4004500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>6941000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3466400</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3668,57 +3850,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2478500</v>
+      </c>
+      <c r="E76" s="3">
         <v>2034300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2148000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1975400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2241000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2441300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2302800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2671400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2815100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2556300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2303900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2396000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2297100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1755500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1624000</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3764,110 +3952,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>588400</v>
+      </c>
+      <c r="E81" s="3">
         <v>495700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>587700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>415300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>634100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>440200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>230200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>200400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>80700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>151900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>155100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>301900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>378800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>518100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>140500</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3886,56 +4083,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>487400</v>
+        <v>439900</v>
       </c>
       <c r="E83" s="3">
+        <v>381300</v>
+      </c>
+      <c r="F83" s="3">
         <v>465100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>552800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>492000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>590600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>787200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>865200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>690900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>956300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>846700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>899200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1007800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>898600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1537900</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1383100</v>
+      </c>
+      <c r="E89" s="3">
         <v>1141100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1321000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1407700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1392200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1526500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1293700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1139800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>961300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1112200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>962800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1128800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1306100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1281300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1418200</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4242,56 +4461,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-620900</v>
+        <v>-718100</v>
       </c>
       <c r="E91" s="3">
+        <v>-582400</v>
+      </c>
+      <c r="F91" s="3">
         <v>-686900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-683400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-666400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-816900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-613500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-824300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1085700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-708500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-672100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-681900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-723300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1166300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-841000</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4385,57 +4611,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-672700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-604700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-668500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-682400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-495300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-893100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-707700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-825900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1095900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-702000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-658800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-650400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>191800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>165100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1210200</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4454,41 +4686,42 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>348500</v>
+      </c>
+      <c r="E96" s="3">
         <v>307400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>276200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>267100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>355700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>315500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>247100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>195900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>93800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-53100</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
@@ -4501,9 +4734,12 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4645,151 +4887,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-646100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-533500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-791800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-771000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-849000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1203400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-621800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-549600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-205500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-124100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-500300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-403700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1155800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-914600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-581200</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E101" s="3">
         <v>300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>2200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-3400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-5600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>5000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-3500</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>63300</v>
+      </c>
+      <c r="E102" s="3">
         <v>3200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-139500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-43400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>46900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-573500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-38000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-235300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-345700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>285500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-191300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>74100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>338200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>525100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-376700</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
